--- a/data/trans_orig/IP16A10-Provincia-trans_orig.xlsx
+++ b/data/trans_orig/IP16A10-Provincia-trans_orig.xlsx
@@ -732,12 +732,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>507</t>
+          <t>519</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>4502</t>
+          <t>4519</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -747,12 +747,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>4,35%</t>
+          <t>4,45%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>38,58%</t>
+          <t>38,73%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -772,7 +772,7 @@
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>2961</t>
+          <t>3537</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -787,7 +787,7 @@
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>24,4%</t>
+          <t>29,15%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -802,12 +802,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>1091</t>
+          <t>1023</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>6235</t>
+          <t>5814</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -817,12 +817,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>4,59%</t>
+          <t>4,3%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>26,19%</t>
+          <t>24,43%</t>
         </is>
       </c>
     </row>
@@ -845,12 +845,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>7166</t>
+          <t>7149</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>11161</t>
+          <t>11149</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -860,12 +860,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>61,42%</t>
+          <t>61,27%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>95,65%</t>
+          <t>95,55%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -880,7 +880,7 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>9174</t>
+          <t>8598</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
@@ -895,7 +895,7 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>75,6%</t>
+          <t>70,85%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
@@ -915,12 +915,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>17568</t>
+          <t>17989</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>22712</t>
+          <t>22780</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -930,12 +930,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>73,81%</t>
+          <t>75,57%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>95,41%</t>
+          <t>95,7%</t>
         </is>
       </c>
     </row>
@@ -1080,7 +1080,7 @@
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>3737</t>
+          <t>3696</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -1095,7 +1095,7 @@
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>22,34%</t>
+          <t>22,09%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -1115,7 +1115,7 @@
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>2636</t>
+          <t>2993</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -1130,7 +1130,7 @@
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>13,28%</t>
+          <t>15,07%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -1145,12 +1145,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>611</t>
+          <t>602</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>4981</t>
+          <t>4987</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -1160,12 +1160,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>1,67%</t>
+          <t>1,65%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>13,62%</t>
+          <t>13,63%</t>
         </is>
       </c>
     </row>
@@ -1188,7 +1188,7 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>12993</t>
+          <t>13034</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
@@ -1203,7 +1203,7 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>77,66%</t>
+          <t>77,91%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
@@ -1223,7 +1223,7 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>17220</t>
+          <t>16863</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
@@ -1238,7 +1238,7 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>86,72%</t>
+          <t>84,93%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
@@ -1258,12 +1258,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>31605</t>
+          <t>31599</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>35975</t>
+          <t>35984</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -1273,12 +1273,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>86,38%</t>
+          <t>86,37%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>98,33%</t>
+          <t>98,35%</t>
         </is>
       </c>
     </row>
@@ -1766,7 +1766,7 @@
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>3286</t>
+          <t>3680</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -1781,7 +1781,7 @@
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>20,1%</t>
+          <t>22,51%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -1801,7 +1801,7 @@
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>3322</t>
+          <t>2826</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -1816,7 +1816,7 @@
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>20,22%</t>
+          <t>17,21%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -1831,12 +1831,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>507</t>
+          <t>514</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>4829</t>
+          <t>4470</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -1846,12 +1846,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>1,55%</t>
+          <t>1,57%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>14,73%</t>
+          <t>13,64%</t>
         </is>
       </c>
     </row>
@@ -1874,7 +1874,7 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>13065</t>
+          <t>12671</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
@@ -1889,7 +1889,7 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>79,9%</t>
+          <t>77,49%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
@@ -1909,7 +1909,7 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>13104</t>
+          <t>13600</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
@@ -1924,7 +1924,7 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>79,78%</t>
+          <t>82,79%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
@@ -1944,12 +1944,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>27948</t>
+          <t>28307</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>32270</t>
+          <t>32263</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -1959,12 +1959,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>85,27%</t>
+          <t>86,36%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>98,45%</t>
+          <t>98,43%</t>
         </is>
       </c>
     </row>
@@ -2452,7 +2452,7 @@
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>3889</t>
+          <t>3069</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
@@ -2467,7 +2467,7 @@
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>31,41%</t>
+          <t>24,79%</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
@@ -2522,7 +2522,7 @@
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>3708</t>
+          <t>2501</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
@@ -2537,7 +2537,7 @@
       </c>
       <c r="W19" s="2" t="inlineStr">
         <is>
-          <t>16,05%</t>
+          <t>10,82%</t>
         </is>
       </c>
     </row>
@@ -2560,7 +2560,7 @@
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>8490</t>
+          <t>9310</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
@@ -2575,7 +2575,7 @@
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>68,59%</t>
+          <t>75,21%</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
@@ -2630,7 +2630,7 @@
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>19400</t>
+          <t>20607</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
@@ -2645,7 +2645,7 @@
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>83,95%</t>
+          <t>89,18%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
@@ -2795,7 +2795,7 @@
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>3332</t>
+          <t>3315</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
@@ -2810,7 +2810,7 @@
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>15,5%</t>
+          <t>15,42%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -2830,7 +2830,7 @@
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>4106</t>
+          <t>3489</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
@@ -2845,7 +2845,7 @@
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>15,48%</t>
+          <t>13,15%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -2865,7 +2865,7 @@
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>4200</t>
+          <t>4591</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
@@ -2880,7 +2880,7 @@
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>8,75%</t>
+          <t>9,56%</t>
         </is>
       </c>
     </row>
@@ -2903,7 +2903,7 @@
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>18167</t>
+          <t>18184</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
@@ -2918,7 +2918,7 @@
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>84,5%</t>
+          <t>84,58%</t>
         </is>
       </c>
       <c r="I23" s="2" t="inlineStr">
@@ -2938,7 +2938,7 @@
       </c>
       <c r="L23" s="2" t="inlineStr">
         <is>
-          <t>22420</t>
+          <t>23037</t>
         </is>
       </c>
       <c r="M23" s="2" t="inlineStr">
@@ -2953,7 +2953,7 @@
       </c>
       <c r="O23" s="2" t="inlineStr">
         <is>
-          <t>84,52%</t>
+          <t>86,85%</t>
         </is>
       </c>
       <c r="P23" s="2" t="inlineStr">
@@ -2973,7 +2973,7 @@
       </c>
       <c r="S23" s="2" t="inlineStr">
         <is>
-          <t>43825</t>
+          <t>43434</t>
         </is>
       </c>
       <c r="T23" s="2" t="inlineStr">
@@ -2988,7 +2988,7 @@
       </c>
       <c r="V23" s="2" t="inlineStr">
         <is>
-          <t>91,25%</t>
+          <t>90,44%</t>
         </is>
       </c>
       <c r="W23" s="2" t="inlineStr">
@@ -3138,7 +3138,7 @@
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>4025</t>
+          <t>3486</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
@@ -3153,7 +3153,7 @@
       </c>
       <c r="I25" s="2" t="inlineStr">
         <is>
-          <t>15,53%</t>
+          <t>13,45%</t>
         </is>
       </c>
       <c r="J25" s="2" t="inlineStr">
@@ -3208,7 +3208,7 @@
       </c>
       <c r="T25" s="2" t="inlineStr">
         <is>
-          <t>3768</t>
+          <t>3671</t>
         </is>
       </c>
       <c r="U25" s="2" t="inlineStr">
@@ -3223,7 +3223,7 @@
       </c>
       <c r="W25" s="2" t="inlineStr">
         <is>
-          <t>5,73%</t>
+          <t>5,58%</t>
         </is>
       </c>
     </row>
@@ -3246,7 +3246,7 @@
       </c>
       <c r="E26" s="2" t="inlineStr">
         <is>
-          <t>21899</t>
+          <t>22438</t>
         </is>
       </c>
       <c r="F26" s="2" t="inlineStr">
@@ -3261,7 +3261,7 @@
       </c>
       <c r="H26" s="2" t="inlineStr">
         <is>
-          <t>84,47%</t>
+          <t>86,55%</t>
         </is>
       </c>
       <c r="I26" s="2" t="inlineStr">
@@ -3316,7 +3316,7 @@
       </c>
       <c r="S26" s="2" t="inlineStr">
         <is>
-          <t>62022</t>
+          <t>62119</t>
         </is>
       </c>
       <c r="T26" s="2" t="inlineStr">
@@ -3331,7 +3331,7 @@
       </c>
       <c r="V26" s="2" t="inlineStr">
         <is>
-          <t>94,27%</t>
+          <t>94,42%</t>
         </is>
       </c>
       <c r="W26" s="2" t="inlineStr">
@@ -3476,12 +3476,12 @@
       </c>
       <c r="E28" s="2" t="inlineStr">
         <is>
-          <t>3459</t>
+          <t>3573</t>
         </is>
       </c>
       <c r="F28" s="2" t="inlineStr">
         <is>
-          <t>11637</t>
+          <t>11072</t>
         </is>
       </c>
       <c r="G28" s="2" t="inlineStr">
@@ -3491,12 +3491,12 @@
       </c>
       <c r="H28" s="2" t="inlineStr">
         <is>
-          <t>2,76%</t>
+          <t>2,85%</t>
         </is>
       </c>
       <c r="I28" s="2" t="inlineStr">
         <is>
-          <t>9,29%</t>
+          <t>8,84%</t>
         </is>
       </c>
       <c r="J28" s="2" t="inlineStr">
@@ -3511,12 +3511,12 @@
       </c>
       <c r="L28" s="2" t="inlineStr">
         <is>
-          <t>669</t>
+          <t>683</t>
         </is>
       </c>
       <c r="M28" s="2" t="inlineStr">
         <is>
-          <t>6158</t>
+          <t>6916</t>
         </is>
       </c>
       <c r="N28" s="2" t="inlineStr">
@@ -3526,12 +3526,12 @@
       </c>
       <c r="O28" s="2" t="inlineStr">
         <is>
-          <t>0,46%</t>
+          <t>0,47%</t>
         </is>
       </c>
       <c r="P28" s="2" t="inlineStr">
         <is>
-          <t>4,28%</t>
+          <t>4,81%</t>
         </is>
       </c>
       <c r="Q28" s="2" t="inlineStr">
@@ -3546,12 +3546,12 @@
       </c>
       <c r="S28" s="2" t="inlineStr">
         <is>
-          <t>5470</t>
+          <t>5721</t>
         </is>
       </c>
       <c r="T28" s="2" t="inlineStr">
         <is>
-          <t>14693</t>
+          <t>14906</t>
         </is>
       </c>
       <c r="U28" s="2" t="inlineStr">
@@ -3561,12 +3561,12 @@
       </c>
       <c r="V28" s="2" t="inlineStr">
         <is>
-          <t>2,03%</t>
+          <t>2,13%</t>
         </is>
       </c>
       <c r="W28" s="2" t="inlineStr">
         <is>
-          <t>5,46%</t>
+          <t>5,54%</t>
         </is>
       </c>
     </row>
@@ -3589,12 +3589,12 @@
       </c>
       <c r="E29" s="2" t="inlineStr">
         <is>
-          <t>113668</t>
+          <t>114233</t>
         </is>
       </c>
       <c r="F29" s="2" t="inlineStr">
         <is>
-          <t>121846</t>
+          <t>121732</t>
         </is>
       </c>
       <c r="G29" s="2" t="inlineStr">
@@ -3604,12 +3604,12 @@
       </c>
       <c r="H29" s="2" t="inlineStr">
         <is>
-          <t>90,71%</t>
+          <t>91,16%</t>
         </is>
       </c>
       <c r="I29" s="2" t="inlineStr">
         <is>
-          <t>97,24%</t>
+          <t>97,15%</t>
         </is>
       </c>
       <c r="J29" s="2" t="inlineStr">
@@ -3624,12 +3624,12 @@
       </c>
       <c r="L29" s="2" t="inlineStr">
         <is>
-          <t>137761</t>
+          <t>137003</t>
         </is>
       </c>
       <c r="M29" s="2" t="inlineStr">
         <is>
-          <t>143250</t>
+          <t>143236</t>
         </is>
       </c>
       <c r="N29" s="2" t="inlineStr">
@@ -3639,12 +3639,12 @@
       </c>
       <c r="O29" s="2" t="inlineStr">
         <is>
-          <t>95,72%</t>
+          <t>95,19%</t>
         </is>
       </c>
       <c r="P29" s="2" t="inlineStr">
         <is>
-          <t>99,54%</t>
+          <t>99,53%</t>
         </is>
       </c>
       <c r="Q29" s="2" t="inlineStr">
@@ -3659,12 +3659,12 @@
       </c>
       <c r="S29" s="2" t="inlineStr">
         <is>
-          <t>254531</t>
+          <t>254318</t>
         </is>
       </c>
       <c r="T29" s="2" t="inlineStr">
         <is>
-          <t>263754</t>
+          <t>263503</t>
         </is>
       </c>
       <c r="U29" s="2" t="inlineStr">
@@ -3674,12 +3674,12 @@
       </c>
       <c r="V29" s="2" t="inlineStr">
         <is>
-          <t>94,54%</t>
+          <t>94,46%</t>
         </is>
       </c>
       <c r="W29" s="2" t="inlineStr">
         <is>
-          <t>97,97%</t>
+          <t>97,87%</t>
         </is>
       </c>
     </row>
@@ -4060,7 +4060,7 @@
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>2641</t>
+          <t>2696</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -4075,7 +4075,7 @@
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>13,86%</t>
+          <t>14,15%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -4095,7 +4095,7 @@
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>3942</t>
+          <t>3863</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -4110,7 +4110,7 @@
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>16,03%</t>
+          <t>15,72%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -4130,7 +4130,7 @@
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>4862</t>
+          <t>4638</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -4145,7 +4145,7 @@
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>11,14%</t>
+          <t>10,63%</t>
         </is>
       </c>
     </row>
@@ -4168,7 +4168,7 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>16419</t>
+          <t>16364</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
@@ -4183,7 +4183,7 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>86,14%</t>
+          <t>85,85%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
@@ -4203,7 +4203,7 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>20641</t>
+          <t>20720</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
@@ -4218,7 +4218,7 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>83,97%</t>
+          <t>84,28%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
@@ -4238,7 +4238,7 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>38782</t>
+          <t>39006</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
@@ -4253,7 +4253,7 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>88,86%</t>
+          <t>89,37%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
@@ -4403,7 +4403,7 @@
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>4089</t>
+          <t>3886</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -4418,7 +4418,7 @@
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>12,41%</t>
+          <t>11,79%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -4438,7 +4438,7 @@
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>2507</t>
+          <t>3155</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -4453,7 +4453,7 @@
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>6,84%</t>
+          <t>8,61%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -4468,12 +4468,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>611</t>
+          <t>596</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>5581</t>
+          <t>4848</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -4483,12 +4483,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>0,88%</t>
+          <t>0,86%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>8,02%</t>
+          <t>6,96%</t>
         </is>
       </c>
     </row>
@@ -4511,7 +4511,7 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>28858</t>
+          <t>29061</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
@@ -4526,7 +4526,7 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>87,59%</t>
+          <t>88,21%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
@@ -4546,7 +4546,7 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>34159</t>
+          <t>33511</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
@@ -4561,7 +4561,7 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>93,16%</t>
+          <t>91,39%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
@@ -4581,12 +4581,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>64032</t>
+          <t>64765</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>69002</t>
+          <t>69017</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -4596,12 +4596,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>91,98%</t>
+          <t>93,04%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>99,12%</t>
+          <t>99,14%</t>
         </is>
       </c>
     </row>
@@ -5467,7 +5467,7 @@
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>4043</t>
+          <t>3945</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -5482,7 +5482,7 @@
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>29,75%</t>
+          <t>29,03%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -5502,7 +5502,7 @@
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>4271</t>
+          <t>4031</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -5517,7 +5517,7 @@
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>12,79%</t>
+          <t>12,07%</t>
         </is>
       </c>
     </row>
@@ -5575,7 +5575,7 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>9544</t>
+          <t>9642</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
@@ -5590,7 +5590,7 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>70,25%</t>
+          <t>70,97%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
@@ -5610,7 +5610,7 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>29129</t>
+          <t>29369</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
@@ -5625,7 +5625,7 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>87,21%</t>
+          <t>87,93%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
@@ -6118,7 +6118,7 @@
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>4907</t>
+          <t>4595</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
@@ -6133,7 +6133,7 @@
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>14,64%</t>
+          <t>13,71%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -6153,7 +6153,7 @@
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>3257</t>
+          <t>3229</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
@@ -6168,7 +6168,7 @@
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>11,16%</t>
+          <t>11,06%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -6188,7 +6188,7 @@
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>6354</t>
+          <t>5459</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
@@ -6203,7 +6203,7 @@
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>10,13%</t>
+          <t>8,71%</t>
         </is>
       </c>
     </row>
@@ -6226,7 +6226,7 @@
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>28604</t>
+          <t>28916</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
@@ -6241,7 +6241,7 @@
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>85,36%</t>
+          <t>86,29%</t>
         </is>
       </c>
       <c r="I23" s="2" t="inlineStr">
@@ -6261,7 +6261,7 @@
       </c>
       <c r="L23" s="2" t="inlineStr">
         <is>
-          <t>25934</t>
+          <t>25962</t>
         </is>
       </c>
       <c r="M23" s="2" t="inlineStr">
@@ -6276,7 +6276,7 @@
       </c>
       <c r="O23" s="2" t="inlineStr">
         <is>
-          <t>88,84%</t>
+          <t>88,94%</t>
         </is>
       </c>
       <c r="P23" s="2" t="inlineStr">
@@ -6296,7 +6296,7 @@
       </c>
       <c r="S23" s="2" t="inlineStr">
         <is>
-          <t>56348</t>
+          <t>57243</t>
         </is>
       </c>
       <c r="T23" s="2" t="inlineStr">
@@ -6311,7 +6311,7 @@
       </c>
       <c r="V23" s="2" t="inlineStr">
         <is>
-          <t>89,87%</t>
+          <t>91,29%</t>
         </is>
       </c>
       <c r="W23" s="2" t="inlineStr">
@@ -6461,7 +6461,7 @@
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>2961</t>
+          <t>3228</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
@@ -6476,7 +6476,7 @@
       </c>
       <c r="I25" s="2" t="inlineStr">
         <is>
-          <t>12,16%</t>
+          <t>13,26%</t>
         </is>
       </c>
       <c r="J25" s="2" t="inlineStr">
@@ -6496,7 +6496,7 @@
       </c>
       <c r="M25" s="2" t="inlineStr">
         <is>
-          <t>3227</t>
+          <t>3262</t>
         </is>
       </c>
       <c r="N25" s="2" t="inlineStr">
@@ -6511,7 +6511,7 @@
       </c>
       <c r="P25" s="2" t="inlineStr">
         <is>
-          <t>12,0%</t>
+          <t>12,12%</t>
         </is>
       </c>
       <c r="Q25" s="2" t="inlineStr">
@@ -6531,7 +6531,7 @@
       </c>
       <c r="T25" s="2" t="inlineStr">
         <is>
-          <t>4020</t>
+          <t>4633</t>
         </is>
       </c>
       <c r="U25" s="2" t="inlineStr">
@@ -6546,7 +6546,7 @@
       </c>
       <c r="W25" s="2" t="inlineStr">
         <is>
-          <t>7,84%</t>
+          <t>9,04%</t>
         </is>
       </c>
     </row>
@@ -6569,7 +6569,7 @@
       </c>
       <c r="E26" s="2" t="inlineStr">
         <is>
-          <t>21389</t>
+          <t>21122</t>
         </is>
       </c>
       <c r="F26" s="2" t="inlineStr">
@@ -6584,7 +6584,7 @@
       </c>
       <c r="H26" s="2" t="inlineStr">
         <is>
-          <t>87,84%</t>
+          <t>86,74%</t>
         </is>
       </c>
       <c r="I26" s="2" t="inlineStr">
@@ -6604,7 +6604,7 @@
       </c>
       <c r="L26" s="2" t="inlineStr">
         <is>
-          <t>23677</t>
+          <t>23642</t>
         </is>
       </c>
       <c r="M26" s="2" t="inlineStr">
@@ -6619,7 +6619,7 @@
       </c>
       <c r="O26" s="2" t="inlineStr">
         <is>
-          <t>88,0%</t>
+          <t>87,88%</t>
         </is>
       </c>
       <c r="P26" s="2" t="inlineStr">
@@ -6639,7 +6639,7 @@
       </c>
       <c r="S26" s="2" t="inlineStr">
         <is>
-          <t>47235</t>
+          <t>46622</t>
         </is>
       </c>
       <c r="T26" s="2" t="inlineStr">
@@ -6654,7 +6654,7 @@
       </c>
       <c r="V26" s="2" t="inlineStr">
         <is>
-          <t>92,16%</t>
+          <t>90,96%</t>
         </is>
       </c>
       <c r="W26" s="2" t="inlineStr">
@@ -6799,12 +6799,12 @@
       </c>
       <c r="E28" s="2" t="inlineStr">
         <is>
-          <t>1123</t>
+          <t>1193</t>
         </is>
       </c>
       <c r="F28" s="2" t="inlineStr">
         <is>
-          <t>7525</t>
+          <t>7245</t>
         </is>
       </c>
       <c r="G28" s="2" t="inlineStr">
@@ -6814,12 +6814,12 @@
       </c>
       <c r="H28" s="2" t="inlineStr">
         <is>
-          <t>0,6%</t>
+          <t>0,64%</t>
         </is>
       </c>
       <c r="I28" s="2" t="inlineStr">
         <is>
-          <t>4,02%</t>
+          <t>3,87%</t>
         </is>
       </c>
       <c r="J28" s="2" t="inlineStr">
@@ -6834,12 +6834,12 @@
       </c>
       <c r="L28" s="2" t="inlineStr">
         <is>
-          <t>1875</t>
+          <t>1314</t>
         </is>
       </c>
       <c r="M28" s="2" t="inlineStr">
         <is>
-          <t>8700</t>
+          <t>8057</t>
         </is>
       </c>
       <c r="N28" s="2" t="inlineStr">
@@ -6849,12 +6849,12 @@
       </c>
       <c r="O28" s="2" t="inlineStr">
         <is>
-          <t>0,98%</t>
+          <t>0,69%</t>
         </is>
       </c>
       <c r="P28" s="2" t="inlineStr">
         <is>
-          <t>4,56%</t>
+          <t>4,22%</t>
         </is>
       </c>
       <c r="Q28" s="2" t="inlineStr">
@@ -6869,12 +6869,12 @@
       </c>
       <c r="S28" s="2" t="inlineStr">
         <is>
-          <t>3667</t>
+          <t>3803</t>
         </is>
       </c>
       <c r="T28" s="2" t="inlineStr">
         <is>
-          <t>13254</t>
+          <t>13004</t>
         </is>
       </c>
       <c r="U28" s="2" t="inlineStr">
@@ -6884,12 +6884,12 @@
       </c>
       <c r="V28" s="2" t="inlineStr">
         <is>
-          <t>0,97%</t>
+          <t>1,01%</t>
         </is>
       </c>
       <c r="W28" s="2" t="inlineStr">
         <is>
-          <t>3,51%</t>
+          <t>3,44%</t>
         </is>
       </c>
     </row>
@@ -6912,12 +6912,12 @@
       </c>
       <c r="E29" s="2" t="inlineStr">
         <is>
-          <t>179467</t>
+          <t>179747</t>
         </is>
       </c>
       <c r="F29" s="2" t="inlineStr">
         <is>
-          <t>185869</t>
+          <t>185799</t>
         </is>
       </c>
       <c r="G29" s="2" t="inlineStr">
@@ -6927,12 +6927,12 @@
       </c>
       <c r="H29" s="2" t="inlineStr">
         <is>
-          <t>95,98%</t>
+          <t>96,13%</t>
         </is>
       </c>
       <c r="I29" s="2" t="inlineStr">
         <is>
-          <t>99,4%</t>
+          <t>99,36%</t>
         </is>
       </c>
       <c r="J29" s="2" t="inlineStr">
@@ -6947,12 +6947,12 @@
       </c>
       <c r="L29" s="2" t="inlineStr">
         <is>
-          <t>182150</t>
+          <t>182793</t>
         </is>
       </c>
       <c r="M29" s="2" t="inlineStr">
         <is>
-          <t>188975</t>
+          <t>189536</t>
         </is>
       </c>
       <c r="N29" s="2" t="inlineStr">
@@ -6962,12 +6962,12 @@
       </c>
       <c r="O29" s="2" t="inlineStr">
         <is>
-          <t>95,44%</t>
+          <t>95,78%</t>
         </is>
       </c>
       <c r="P29" s="2" t="inlineStr">
         <is>
-          <t>99,02%</t>
+          <t>99,31%</t>
         </is>
       </c>
       <c r="Q29" s="2" t="inlineStr">
@@ -6982,12 +6982,12 @@
       </c>
       <c r="S29" s="2" t="inlineStr">
         <is>
-          <t>364588</t>
+          <t>364838</t>
         </is>
       </c>
       <c r="T29" s="2" t="inlineStr">
         <is>
-          <t>374175</t>
+          <t>374039</t>
         </is>
       </c>
       <c r="U29" s="2" t="inlineStr">
@@ -6997,12 +6997,12 @@
       </c>
       <c r="V29" s="2" t="inlineStr">
         <is>
-          <t>96,49%</t>
+          <t>96,56%</t>
         </is>
       </c>
       <c r="W29" s="2" t="inlineStr">
         <is>
-          <t>99,03%</t>
+          <t>98,99%</t>
         </is>
       </c>
     </row>
@@ -7761,7 +7761,7 @@
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>4878</t>
+          <t>4298</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -7776,7 +7776,7 @@
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>20,92%</t>
+          <t>18,43%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -7796,7 +7796,7 @@
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>4495</t>
+          <t>4868</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -7811,7 +7811,7 @@
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>8,37%</t>
+          <t>9,06%</t>
         </is>
       </c>
     </row>
@@ -7869,7 +7869,7 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>18440</t>
+          <t>19020</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
@@ -7884,7 +7884,7 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>79,08%</t>
+          <t>81,57%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
@@ -7904,7 +7904,7 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>49236</t>
+          <t>48863</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
@@ -7919,7 +7919,7 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>91,63%</t>
+          <t>90,94%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
@@ -8412,7 +8412,7 @@
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>4924</t>
+          <t>3654</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -8427,7 +8427,7 @@
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>14,1%</t>
+          <t>10,47%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -8447,7 +8447,7 @@
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>2849</t>
+          <t>3271</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -8462,7 +8462,7 @@
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>9,62%</t>
+          <t>11,05%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -8477,12 +8477,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>559</t>
+          <t>550</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>5437</t>
+          <t>5125</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -8492,12 +8492,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>0,87%</t>
+          <t>0,85%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>8,43%</t>
+          <t>7,94%</t>
         </is>
       </c>
     </row>
@@ -8520,7 +8520,7 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>29991</t>
+          <t>31261</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
@@ -8535,7 +8535,7 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>85,9%</t>
+          <t>89,53%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
@@ -8555,7 +8555,7 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>26763</t>
+          <t>26341</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
@@ -8570,7 +8570,7 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>90,38%</t>
+          <t>88,95%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
@@ -8590,12 +8590,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>59090</t>
+          <t>59402</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>63968</t>
+          <t>63977</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -8605,12 +8605,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>91,57%</t>
+          <t>92,06%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>99,13%</t>
+          <t>99,15%</t>
         </is>
       </c>
     </row>
@@ -9441,7 +9441,7 @@
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>3187</t>
+          <t>3102</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
@@ -9456,7 +9456,7 @@
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>16,16%</t>
+          <t>15,73%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -9511,7 +9511,7 @@
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>3157</t>
+          <t>3065</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
@@ -9526,7 +9526,7 @@
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>9,37%</t>
+          <t>9,1%</t>
         </is>
       </c>
     </row>
@@ -9549,7 +9549,7 @@
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>16526</t>
+          <t>16611</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
@@ -9564,7 +9564,7 @@
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>83,84%</t>
+          <t>84,27%</t>
         </is>
       </c>
       <c r="I23" s="2" t="inlineStr">
@@ -9619,7 +9619,7 @@
       </c>
       <c r="S23" s="2" t="inlineStr">
         <is>
-          <t>30520</t>
+          <t>30612</t>
         </is>
       </c>
       <c r="T23" s="2" t="inlineStr">
@@ -9634,7 +9634,7 @@
       </c>
       <c r="V23" s="2" t="inlineStr">
         <is>
-          <t>90,63%</t>
+          <t>90,9%</t>
         </is>
       </c>
       <c r="W23" s="2" t="inlineStr">
@@ -10122,12 +10122,12 @@
       </c>
       <c r="E28" s="2" t="inlineStr">
         <is>
-          <t>558</t>
+          <t>557</t>
         </is>
       </c>
       <c r="F28" s="2" t="inlineStr">
         <is>
-          <t>4656</t>
+          <t>4794</t>
         </is>
       </c>
       <c r="G28" s="2" t="inlineStr">
@@ -10142,7 +10142,7 @@
       </c>
       <c r="I28" s="2" t="inlineStr">
         <is>
-          <t>2,86%</t>
+          <t>2,95%</t>
         </is>
       </c>
       <c r="J28" s="2" t="inlineStr">
@@ -10157,12 +10157,12 @@
       </c>
       <c r="L28" s="2" t="inlineStr">
         <is>
-          <t>659</t>
+          <t>656</t>
         </is>
       </c>
       <c r="M28" s="2" t="inlineStr">
         <is>
-          <t>5451</t>
+          <t>5618</t>
         </is>
       </c>
       <c r="N28" s="2" t="inlineStr">
@@ -10177,7 +10177,7 @@
       </c>
       <c r="P28" s="2" t="inlineStr">
         <is>
-          <t>3,68%</t>
+          <t>3,79%</t>
         </is>
       </c>
       <c r="Q28" s="2" t="inlineStr">
@@ -10192,12 +10192,12 @@
       </c>
       <c r="S28" s="2" t="inlineStr">
         <is>
-          <t>1349</t>
+          <t>1393</t>
         </is>
       </c>
       <c r="T28" s="2" t="inlineStr">
         <is>
-          <t>7953</t>
+          <t>7846</t>
         </is>
       </c>
       <c r="U28" s="2" t="inlineStr">
@@ -10207,12 +10207,12 @@
       </c>
       <c r="V28" s="2" t="inlineStr">
         <is>
-          <t>0,43%</t>
+          <t>0,45%</t>
         </is>
       </c>
       <c r="W28" s="2" t="inlineStr">
         <is>
-          <t>2,56%</t>
+          <t>2,53%</t>
         </is>
       </c>
     </row>
@@ -10235,12 +10235,12 @@
       </c>
       <c r="E29" s="2" t="inlineStr">
         <is>
-          <t>157880</t>
+          <t>157742</t>
         </is>
       </c>
       <c r="F29" s="2" t="inlineStr">
         <is>
-          <t>161978</t>
+          <t>161979</t>
         </is>
       </c>
       <c r="G29" s="2" t="inlineStr">
@@ -10250,7 +10250,7 @@
       </c>
       <c r="H29" s="2" t="inlineStr">
         <is>
-          <t>97,14%</t>
+          <t>97,05%</t>
         </is>
       </c>
       <c r="I29" s="2" t="inlineStr">
@@ -10270,12 +10270,12 @@
       </c>
       <c r="L29" s="2" t="inlineStr">
         <is>
-          <t>142674</t>
+          <t>142507</t>
         </is>
       </c>
       <c r="M29" s="2" t="inlineStr">
         <is>
-          <t>147466</t>
+          <t>147469</t>
         </is>
       </c>
       <c r="N29" s="2" t="inlineStr">
@@ -10285,7 +10285,7 @@
       </c>
       <c r="O29" s="2" t="inlineStr">
         <is>
-          <t>96,32%</t>
+          <t>96,21%</t>
         </is>
       </c>
       <c r="P29" s="2" t="inlineStr">
@@ -10305,12 +10305,12 @@
       </c>
       <c r="S29" s="2" t="inlineStr">
         <is>
-          <t>302708</t>
+          <t>302815</t>
         </is>
       </c>
       <c r="T29" s="2" t="inlineStr">
         <is>
-          <t>309312</t>
+          <t>309268</t>
         </is>
       </c>
       <c r="U29" s="2" t="inlineStr">
@@ -10320,12 +10320,12 @@
       </c>
       <c r="V29" s="2" t="inlineStr">
         <is>
-          <t>97,44%</t>
+          <t>97,47%</t>
         </is>
       </c>
       <c r="W29" s="2" t="inlineStr">
         <is>
-          <t>99,57%</t>
+          <t>99,55%</t>
         </is>
       </c>
     </row>

--- a/data/trans_orig/IP16A10-Provincia-trans_orig.xlsx
+++ b/data/trans_orig/IP16A10-Provincia-trans_orig.xlsx
@@ -543,7 +543,7 @@
       <c r="B1" s="2" t="n"/>
       <c r="C1" s="3" t="inlineStr">
         <is>
-          <t>Niña</t>
+          <t>Niño</t>
         </is>
       </c>
       <c r="D1" s="3" t="n"/>
@@ -554,7 +554,7 @@
       <c r="I1" s="3" t="n"/>
       <c r="J1" s="3" t="inlineStr">
         <is>
-          <t>Niño</t>
+          <t>Niña</t>
         </is>
       </c>
       <c r="K1" s="3" t="n"/>
@@ -722,72 +722,72 @@
       </c>
       <c r="C4" s="2" t="inlineStr">
         <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="D4" s="2" t="inlineStr">
+        <is>
+          <t>685</t>
+        </is>
+      </c>
+      <c r="E4" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="F4" s="2" t="inlineStr">
+        <is>
+          <t>3522</t>
+        </is>
+      </c>
+      <c r="G4" s="2" t="inlineStr">
+        <is>
+          <t>5,65%</t>
+        </is>
+      </c>
+      <c r="H4" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="I4" s="2" t="inlineStr">
+        <is>
+          <t>29,02%</t>
+        </is>
+      </c>
+      <c r="J4" s="2" t="inlineStr">
+        <is>
           <t>4</t>
         </is>
       </c>
-      <c r="D4" s="2" t="inlineStr">
+      <c r="K4" s="2" t="inlineStr">
         <is>
           <t>2137</t>
         </is>
       </c>
-      <c r="E4" s="2" t="inlineStr">
-        <is>
-          <t>519</t>
-        </is>
-      </c>
-      <c r="F4" s="2" t="inlineStr">
-        <is>
-          <t>4519</t>
-        </is>
-      </c>
-      <c r="G4" s="2" t="inlineStr">
+      <c r="L4" s="2" t="inlineStr">
+        <is>
+          <t>508</t>
+        </is>
+      </c>
+      <c r="M4" s="2" t="inlineStr">
+        <is>
+          <t>4527</t>
+        </is>
+      </c>
+      <c r="N4" s="2" t="inlineStr">
         <is>
           <t>18,32%</t>
         </is>
       </c>
-      <c r="H4" s="2" t="inlineStr">
-        <is>
-          <t>4,45%</t>
-        </is>
-      </c>
-      <c r="I4" s="2" t="inlineStr">
-        <is>
-          <t>38,73%</t>
-        </is>
-      </c>
-      <c r="J4" s="2" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="K4" s="2" t="inlineStr">
-        <is>
-          <t>685</t>
-        </is>
-      </c>
-      <c r="L4" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="M4" s="2" t="inlineStr">
-        <is>
-          <t>3537</t>
-        </is>
-      </c>
-      <c r="N4" s="2" t="inlineStr">
-        <is>
-          <t>5,65%</t>
-        </is>
-      </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>4,36%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>29,15%</t>
+          <t>38,8%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -802,12 +802,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>1023</t>
+          <t>1046</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>5814</t>
+          <t>6003</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -817,12 +817,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>4,3%</t>
+          <t>4,4%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>24,43%</t>
+          <t>25,22%</t>
         </is>
       </c>
     </row>
@@ -835,72 +835,72 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
+          <t>16</t>
+        </is>
+      </c>
+      <c r="D5" s="2" t="inlineStr">
+        <is>
+          <t>11450</t>
+        </is>
+      </c>
+      <c r="E5" s="2" t="inlineStr">
+        <is>
+          <t>8613</t>
+        </is>
+      </c>
+      <c r="F5" s="2" t="inlineStr">
+        <is>
+          <t>12135</t>
+        </is>
+      </c>
+      <c r="G5" s="2" t="inlineStr">
+        <is>
+          <t>94,35%</t>
+        </is>
+      </c>
+      <c r="H5" s="2" t="inlineStr">
+        <is>
+          <t>70,98%</t>
+        </is>
+      </c>
+      <c r="I5" s="2" t="inlineStr">
+        <is>
+          <t>100,0%</t>
+        </is>
+      </c>
+      <c r="J5" s="2" t="inlineStr">
+        <is>
           <t>15</t>
         </is>
       </c>
-      <c r="D5" s="2" t="inlineStr">
+      <c r="K5" s="2" t="inlineStr">
         <is>
           <t>9531</t>
         </is>
       </c>
-      <c r="E5" s="2" t="inlineStr">
-        <is>
-          <t>7149</t>
-        </is>
-      </c>
-      <c r="F5" s="2" t="inlineStr">
-        <is>
-          <t>11149</t>
-        </is>
-      </c>
-      <c r="G5" s="2" t="inlineStr">
+      <c r="L5" s="2" t="inlineStr">
+        <is>
+          <t>7141</t>
+        </is>
+      </c>
+      <c r="M5" s="2" t="inlineStr">
+        <is>
+          <t>11160</t>
+        </is>
+      </c>
+      <c r="N5" s="2" t="inlineStr">
         <is>
           <t>81,68%</t>
         </is>
       </c>
-      <c r="H5" s="2" t="inlineStr">
-        <is>
-          <t>61,27%</t>
-        </is>
-      </c>
-      <c r="I5" s="2" t="inlineStr">
-        <is>
-          <t>95,55%</t>
-        </is>
-      </c>
-      <c r="J5" s="2" t="inlineStr">
-        <is>
-          <t>16</t>
-        </is>
-      </c>
-      <c r="K5" s="2" t="inlineStr">
-        <is>
-          <t>11450</t>
-        </is>
-      </c>
-      <c r="L5" s="2" t="inlineStr">
-        <is>
-          <t>8598</t>
-        </is>
-      </c>
-      <c r="M5" s="2" t="inlineStr">
-        <is>
-          <t>12135</t>
-        </is>
-      </c>
-      <c r="N5" s="2" t="inlineStr">
-        <is>
-          <t>94,35%</t>
-        </is>
-      </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>70,85%</t>
+          <t>61,2%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>100,0%</t>
+          <t>95,64%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -915,12 +915,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>17989</t>
+          <t>17800</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>22780</t>
+          <t>22757</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -930,12 +930,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>75,57%</t>
+          <t>74,78%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>95,7%</t>
+          <t>95,6%</t>
         </is>
       </c>
     </row>
@@ -948,57 +948,57 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
+          <t>17</t>
+        </is>
+      </c>
+      <c r="D6" s="2" t="inlineStr">
+        <is>
+          <t>12135</t>
+        </is>
+      </c>
+      <c r="E6" s="2" t="inlineStr">
+        <is>
+          <t>12135</t>
+        </is>
+      </c>
+      <c r="F6" s="2" t="inlineStr">
+        <is>
+          <t>12135</t>
+        </is>
+      </c>
+      <c r="G6" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H6" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I6" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J6" s="2" t="inlineStr">
+        <is>
           <t>19</t>
         </is>
       </c>
-      <c r="D6" s="2" t="inlineStr">
+      <c r="K6" s="2" t="inlineStr">
         <is>
           <t>11668</t>
         </is>
       </c>
-      <c r="E6" s="2" t="inlineStr">
+      <c r="L6" s="2" t="inlineStr">
         <is>
           <t>11668</t>
         </is>
       </c>
-      <c r="F6" s="2" t="inlineStr">
+      <c r="M6" s="2" t="inlineStr">
         <is>
           <t>11668</t>
-        </is>
-      </c>
-      <c r="G6" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H6" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I6" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J6" s="2" t="inlineStr">
-        <is>
-          <t>17</t>
-        </is>
-      </c>
-      <c r="K6" s="2" t="inlineStr">
-        <is>
-          <t>12135</t>
-        </is>
-      </c>
-      <c r="L6" s="2" t="inlineStr">
-        <is>
-          <t>12135</t>
-        </is>
-      </c>
-      <c r="M6" s="2" t="inlineStr">
-        <is>
-          <t>12135</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
@@ -1065,72 +1065,72 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="D7" s="2" t="inlineStr">
+        <is>
+          <t>642</t>
+        </is>
+      </c>
+      <c r="E7" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="F7" s="2" t="inlineStr">
+        <is>
+          <t>3378</t>
+        </is>
+      </c>
+      <c r="G7" s="2" t="inlineStr">
+        <is>
+          <t>3,23%</t>
+        </is>
+      </c>
+      <c r="H7" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="I7" s="2" t="inlineStr">
+        <is>
+          <t>17,01%</t>
+        </is>
+      </c>
+      <c r="J7" s="2" t="inlineStr">
+        <is>
           <t>2</t>
         </is>
       </c>
-      <c r="D7" s="2" t="inlineStr">
+      <c r="K7" s="2" t="inlineStr">
         <is>
           <t>1225</t>
         </is>
       </c>
-      <c r="E7" s="2" t="inlineStr">
+      <c r="L7" s="2" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="F7" s="2" t="inlineStr">
-        <is>
-          <t>3696</t>
-        </is>
-      </c>
-      <c r="G7" s="2" t="inlineStr">
+      <c r="M7" s="2" t="inlineStr">
+        <is>
+          <t>3697</t>
+        </is>
+      </c>
+      <c r="N7" s="2" t="inlineStr">
         <is>
           <t>7,33%</t>
         </is>
       </c>
-      <c r="H7" s="2" t="inlineStr">
+      <c r="O7" s="2" t="inlineStr">
         <is>
           <t>0,0%</t>
         </is>
       </c>
-      <c r="I7" s="2" t="inlineStr">
-        <is>
-          <t>22,09%</t>
-        </is>
-      </c>
-      <c r="J7" s="2" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="K7" s="2" t="inlineStr">
-        <is>
-          <t>642</t>
-        </is>
-      </c>
-      <c r="L7" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="M7" s="2" t="inlineStr">
-        <is>
-          <t>2993</t>
-        </is>
-      </c>
-      <c r="N7" s="2" t="inlineStr">
-        <is>
-          <t>3,23%</t>
-        </is>
-      </c>
-      <c r="O7" s="2" t="inlineStr">
-        <is>
-          <t>0,0%</t>
-        </is>
-      </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>15,07%</t>
+          <t>22,1%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -1145,12 +1145,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>602</t>
+          <t>610</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>4987</t>
+          <t>5082</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -1160,12 +1160,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>1,65%</t>
+          <t>1,67%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>13,63%</t>
+          <t>13,89%</t>
         </is>
       </c>
     </row>
@@ -1178,74 +1178,74 @@
       </c>
       <c r="C8" s="2" t="inlineStr">
         <is>
+          <t>29</t>
+        </is>
+      </c>
+      <c r="D8" s="2" t="inlineStr">
+        <is>
+          <t>19214</t>
+        </is>
+      </c>
+      <c r="E8" s="2" t="inlineStr">
+        <is>
+          <t>16478</t>
+        </is>
+      </c>
+      <c r="F8" s="2" t="inlineStr">
+        <is>
+          <t>19856</t>
+        </is>
+      </c>
+      <c r="G8" s="2" t="inlineStr">
+        <is>
+          <t>96,77%</t>
+        </is>
+      </c>
+      <c r="H8" s="2" t="inlineStr">
+        <is>
+          <t>82,99%</t>
+        </is>
+      </c>
+      <c r="I8" s="2" t="inlineStr">
+        <is>
+          <t>100,0%</t>
+        </is>
+      </c>
+      <c r="J8" s="2" t="inlineStr">
+        <is>
           <t>25</t>
         </is>
       </c>
-      <c r="D8" s="2" t="inlineStr">
+      <c r="K8" s="2" t="inlineStr">
         <is>
           <t>15505</t>
         </is>
       </c>
-      <c r="E8" s="2" t="inlineStr">
-        <is>
-          <t>13034</t>
-        </is>
-      </c>
-      <c r="F8" s="2" t="inlineStr">
+      <c r="L8" s="2" t="inlineStr">
+        <is>
+          <t>13033</t>
+        </is>
+      </c>
+      <c r="M8" s="2" t="inlineStr">
         <is>
           <t>16730</t>
         </is>
       </c>
-      <c r="G8" s="2" t="inlineStr">
+      <c r="N8" s="2" t="inlineStr">
         <is>
           <t>92,67%</t>
         </is>
       </c>
-      <c r="H8" s="2" t="inlineStr">
-        <is>
-          <t>77,91%</t>
-        </is>
-      </c>
-      <c r="I8" s="2" t="inlineStr">
+      <c r="O8" s="2" t="inlineStr">
+        <is>
+          <t>77,9%</t>
+        </is>
+      </c>
+      <c r="P8" s="2" t="inlineStr">
         <is>
           <t>100,0%</t>
         </is>
       </c>
-      <c r="J8" s="2" t="inlineStr">
-        <is>
-          <t>29</t>
-        </is>
-      </c>
-      <c r="K8" s="2" t="inlineStr">
-        <is>
-          <t>19214</t>
-        </is>
-      </c>
-      <c r="L8" s="2" t="inlineStr">
-        <is>
-          <t>16863</t>
-        </is>
-      </c>
-      <c r="M8" s="2" t="inlineStr">
-        <is>
-          <t>19856</t>
-        </is>
-      </c>
-      <c r="N8" s="2" t="inlineStr">
-        <is>
-          <t>96,77%</t>
-        </is>
-      </c>
-      <c r="O8" s="2" t="inlineStr">
-        <is>
-          <t>84,93%</t>
-        </is>
-      </c>
-      <c r="P8" s="2" t="inlineStr">
-        <is>
-          <t>100,0%</t>
-        </is>
-      </c>
       <c r="Q8" s="2" t="inlineStr">
         <is>
           <t>54</t>
@@ -1258,12 +1258,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>31599</t>
+          <t>31504</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>35984</t>
+          <t>35976</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -1273,12 +1273,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>86,37%</t>
+          <t>86,11%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>98,35%</t>
+          <t>98,33%</t>
         </is>
       </c>
     </row>
@@ -1291,57 +1291,57 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
+          <t>30</t>
+        </is>
+      </c>
+      <c r="D9" s="2" t="inlineStr">
+        <is>
+          <t>19856</t>
+        </is>
+      </c>
+      <c r="E9" s="2" t="inlineStr">
+        <is>
+          <t>19856</t>
+        </is>
+      </c>
+      <c r="F9" s="2" t="inlineStr">
+        <is>
+          <t>19856</t>
+        </is>
+      </c>
+      <c r="G9" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H9" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I9" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J9" s="2" t="inlineStr">
+        <is>
           <t>27</t>
         </is>
       </c>
-      <c r="D9" s="2" t="inlineStr">
+      <c r="K9" s="2" t="inlineStr">
         <is>
           <t>16730</t>
         </is>
       </c>
-      <c r="E9" s="2" t="inlineStr">
+      <c r="L9" s="2" t="inlineStr">
         <is>
           <t>16730</t>
         </is>
       </c>
-      <c r="F9" s="2" t="inlineStr">
+      <c r="M9" s="2" t="inlineStr">
         <is>
           <t>16730</t>
-        </is>
-      </c>
-      <c r="G9" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H9" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I9" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J9" s="2" t="inlineStr">
-        <is>
-          <t>30</t>
-        </is>
-      </c>
-      <c r="K9" s="2" t="inlineStr">
-        <is>
-          <t>19856</t>
-        </is>
-      </c>
-      <c r="L9" s="2" t="inlineStr">
-        <is>
-          <t>19856</t>
-        </is>
-      </c>
-      <c r="M9" s="2" t="inlineStr">
-        <is>
-          <t>19856</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
@@ -1521,47 +1521,47 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
+          <t>17</t>
+        </is>
+      </c>
+      <c r="D11" s="2" t="inlineStr">
+        <is>
+          <t>10561</t>
+        </is>
+      </c>
+      <c r="E11" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="F11" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G11" s="2" t="inlineStr">
+        <is>
+          <t>100,0%</t>
+        </is>
+      </c>
+      <c r="H11" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="I11" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="J11" s="2" t="inlineStr">
+        <is>
           <t>16</t>
         </is>
       </c>
-      <c r="D11" s="2" t="inlineStr">
+      <c r="K11" s="2" t="inlineStr">
         <is>
           <t>11627</t>
-        </is>
-      </c>
-      <c r="E11" s="2" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="F11" s="2" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="G11" s="2" t="inlineStr">
-        <is>
-          <t>100,0%</t>
-        </is>
-      </c>
-      <c r="H11" s="2" t="inlineStr">
-        <is>
-          <t>—%</t>
-        </is>
-      </c>
-      <c r="I11" s="2" t="inlineStr">
-        <is>
-          <t>—%</t>
-        </is>
-      </c>
-      <c r="J11" s="2" t="inlineStr">
-        <is>
-          <t>17</t>
-        </is>
-      </c>
-      <c r="K11" s="2" t="inlineStr">
-        <is>
-          <t>10561</t>
         </is>
       </c>
       <c r="L11" s="2" t="inlineStr">
@@ -1634,57 +1634,57 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
+          <t>17</t>
+        </is>
+      </c>
+      <c r="D12" s="2" t="inlineStr">
+        <is>
+          <t>10561</t>
+        </is>
+      </c>
+      <c r="E12" s="2" t="inlineStr">
+        <is>
+          <t>10561</t>
+        </is>
+      </c>
+      <c r="F12" s="2" t="inlineStr">
+        <is>
+          <t>10561</t>
+        </is>
+      </c>
+      <c r="G12" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H12" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I12" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J12" s="2" t="inlineStr">
+        <is>
           <t>16</t>
         </is>
       </c>
-      <c r="D12" s="2" t="inlineStr">
+      <c r="K12" s="2" t="inlineStr">
         <is>
           <t>11627</t>
         </is>
       </c>
-      <c r="E12" s="2" t="inlineStr">
+      <c r="L12" s="2" t="inlineStr">
         <is>
           <t>11627</t>
         </is>
       </c>
-      <c r="F12" s="2" t="inlineStr">
+      <c r="M12" s="2" t="inlineStr">
         <is>
           <t>11627</t>
-        </is>
-      </c>
-      <c r="G12" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H12" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I12" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J12" s="2" t="inlineStr">
-        <is>
-          <t>17</t>
-        </is>
-      </c>
-      <c r="K12" s="2" t="inlineStr">
-        <is>
-          <t>10561</t>
-        </is>
-      </c>
-      <c r="L12" s="2" t="inlineStr">
-        <is>
-          <t>10561</t>
-        </is>
-      </c>
-      <c r="M12" s="2" t="inlineStr">
-        <is>
-          <t>10561</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
@@ -1751,72 +1751,72 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="D13" s="2" t="inlineStr">
+        <is>
+          <t>667</t>
+        </is>
+      </c>
+      <c r="E13" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="F13" s="2" t="inlineStr">
+        <is>
+          <t>3301</t>
+        </is>
+      </c>
+      <c r="G13" s="2" t="inlineStr">
+        <is>
+          <t>4,06%</t>
+        </is>
+      </c>
+      <c r="H13" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="I13" s="2" t="inlineStr">
+        <is>
+          <t>20,09%</t>
+        </is>
+      </c>
+      <c r="J13" s="2" t="inlineStr">
+        <is>
           <t>2</t>
         </is>
       </c>
-      <c r="D13" s="2" t="inlineStr">
+      <c r="K13" s="2" t="inlineStr">
         <is>
           <t>1047</t>
         </is>
       </c>
-      <c r="E13" s="2" t="inlineStr">
+      <c r="L13" s="2" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="F13" s="2" t="inlineStr">
-        <is>
-          <t>3680</t>
-        </is>
-      </c>
-      <c r="G13" s="2" t="inlineStr">
+      <c r="M13" s="2" t="inlineStr">
+        <is>
+          <t>3422</t>
+        </is>
+      </c>
+      <c r="N13" s="2" t="inlineStr">
         <is>
           <t>6,4%</t>
         </is>
       </c>
-      <c r="H13" s="2" t="inlineStr">
+      <c r="O13" s="2" t="inlineStr">
         <is>
           <t>0,0%</t>
         </is>
       </c>
-      <c r="I13" s="2" t="inlineStr">
-        <is>
-          <t>22,51%</t>
-        </is>
-      </c>
-      <c r="J13" s="2" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="K13" s="2" t="inlineStr">
-        <is>
-          <t>667</t>
-        </is>
-      </c>
-      <c r="L13" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="M13" s="2" t="inlineStr">
-        <is>
-          <t>2826</t>
-        </is>
-      </c>
-      <c r="N13" s="2" t="inlineStr">
-        <is>
-          <t>4,06%</t>
-        </is>
-      </c>
-      <c r="O13" s="2" t="inlineStr">
-        <is>
-          <t>0,0%</t>
-        </is>
-      </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>17,21%</t>
+          <t>20,93%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -1836,7 +1836,7 @@
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>4470</t>
+          <t>4638</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -1851,7 +1851,7 @@
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>13,64%</t>
+          <t>14,15%</t>
         </is>
       </c>
     </row>
@@ -1869,69 +1869,69 @@
       </c>
       <c r="D14" s="2" t="inlineStr">
         <is>
+          <t>15759</t>
+        </is>
+      </c>
+      <c r="E14" s="2" t="inlineStr">
+        <is>
+          <t>13125</t>
+        </is>
+      </c>
+      <c r="F14" s="2" t="inlineStr">
+        <is>
+          <t>16426</t>
+        </is>
+      </c>
+      <c r="G14" s="2" t="inlineStr">
+        <is>
+          <t>95,94%</t>
+        </is>
+      </c>
+      <c r="H14" s="2" t="inlineStr">
+        <is>
+          <t>79,91%</t>
+        </is>
+      </c>
+      <c r="I14" s="2" t="inlineStr">
+        <is>
+          <t>100,0%</t>
+        </is>
+      </c>
+      <c r="J14" s="2" t="inlineStr">
+        <is>
+          <t>22</t>
+        </is>
+      </c>
+      <c r="K14" s="2" t="inlineStr">
+        <is>
           <t>15304</t>
         </is>
       </c>
-      <c r="E14" s="2" t="inlineStr">
-        <is>
-          <t>12671</t>
-        </is>
-      </c>
-      <c r="F14" s="2" t="inlineStr">
+      <c r="L14" s="2" t="inlineStr">
+        <is>
+          <t>12929</t>
+        </is>
+      </c>
+      <c r="M14" s="2" t="inlineStr">
         <is>
           <t>16351</t>
         </is>
       </c>
-      <c r="G14" s="2" t="inlineStr">
+      <c r="N14" s="2" t="inlineStr">
         <is>
           <t>93,6%</t>
         </is>
       </c>
-      <c r="H14" s="2" t="inlineStr">
-        <is>
-          <t>77,49%</t>
-        </is>
-      </c>
-      <c r="I14" s="2" t="inlineStr">
+      <c r="O14" s="2" t="inlineStr">
+        <is>
+          <t>79,07%</t>
+        </is>
+      </c>
+      <c r="P14" s="2" t="inlineStr">
         <is>
           <t>100,0%</t>
         </is>
       </c>
-      <c r="J14" s="2" t="inlineStr">
-        <is>
-          <t>22</t>
-        </is>
-      </c>
-      <c r="K14" s="2" t="inlineStr">
-        <is>
-          <t>15759</t>
-        </is>
-      </c>
-      <c r="L14" s="2" t="inlineStr">
-        <is>
-          <t>13600</t>
-        </is>
-      </c>
-      <c r="M14" s="2" t="inlineStr">
-        <is>
-          <t>16426</t>
-        </is>
-      </c>
-      <c r="N14" s="2" t="inlineStr">
-        <is>
-          <t>95,94%</t>
-        </is>
-      </c>
-      <c r="O14" s="2" t="inlineStr">
-        <is>
-          <t>82,79%</t>
-        </is>
-      </c>
-      <c r="P14" s="2" t="inlineStr">
-        <is>
-          <t>100,0%</t>
-        </is>
-      </c>
       <c r="Q14" s="2" t="inlineStr">
         <is>
           <t>44</t>
@@ -1944,7 +1944,7 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>28307</t>
+          <t>28139</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
@@ -1959,7 +1959,7 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>86,36%</t>
+          <t>85,85%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
@@ -1977,57 +1977,57 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
+          <t>23</t>
+        </is>
+      </c>
+      <c r="D15" s="2" t="inlineStr">
+        <is>
+          <t>16426</t>
+        </is>
+      </c>
+      <c r="E15" s="2" t="inlineStr">
+        <is>
+          <t>16426</t>
+        </is>
+      </c>
+      <c r="F15" s="2" t="inlineStr">
+        <is>
+          <t>16426</t>
+        </is>
+      </c>
+      <c r="G15" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H15" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I15" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J15" s="2" t="inlineStr">
+        <is>
           <t>24</t>
         </is>
       </c>
-      <c r="D15" s="2" t="inlineStr">
+      <c r="K15" s="2" t="inlineStr">
         <is>
           <t>16351</t>
         </is>
       </c>
-      <c r="E15" s="2" t="inlineStr">
+      <c r="L15" s="2" t="inlineStr">
         <is>
           <t>16351</t>
         </is>
       </c>
-      <c r="F15" s="2" t="inlineStr">
+      <c r="M15" s="2" t="inlineStr">
         <is>
           <t>16351</t>
-        </is>
-      </c>
-      <c r="G15" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H15" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I15" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J15" s="2" t="inlineStr">
-        <is>
-          <t>23</t>
-        </is>
-      </c>
-      <c r="K15" s="2" t="inlineStr">
-        <is>
-          <t>16426</t>
-        </is>
-      </c>
-      <c r="L15" s="2" t="inlineStr">
-        <is>
-          <t>16426</t>
-        </is>
-      </c>
-      <c r="M15" s="2" t="inlineStr">
-        <is>
-          <t>16426</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
@@ -2207,47 +2207,47 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
+          <t>11</t>
+        </is>
+      </c>
+      <c r="D17" s="2" t="inlineStr">
+        <is>
+          <t>7820</t>
+        </is>
+      </c>
+      <c r="E17" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="F17" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G17" s="2" t="inlineStr">
+        <is>
+          <t>100,0%</t>
+        </is>
+      </c>
+      <c r="H17" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="I17" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="J17" s="2" t="inlineStr">
+        <is>
           <t>13</t>
         </is>
       </c>
-      <c r="D17" s="2" t="inlineStr">
+      <c r="K17" s="2" t="inlineStr">
         <is>
           <t>9126</t>
-        </is>
-      </c>
-      <c r="E17" s="2" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="F17" s="2" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="G17" s="2" t="inlineStr">
-        <is>
-          <t>100,0%</t>
-        </is>
-      </c>
-      <c r="H17" s="2" t="inlineStr">
-        <is>
-          <t>—%</t>
-        </is>
-      </c>
-      <c r="I17" s="2" t="inlineStr">
-        <is>
-          <t>—%</t>
-        </is>
-      </c>
-      <c r="J17" s="2" t="inlineStr">
-        <is>
-          <t>11</t>
-        </is>
-      </c>
-      <c r="K17" s="2" t="inlineStr">
-        <is>
-          <t>7820</t>
         </is>
       </c>
       <c r="L17" s="2" t="inlineStr">
@@ -2320,57 +2320,57 @@
       </c>
       <c r="C18" s="2" t="inlineStr">
         <is>
+          <t>11</t>
+        </is>
+      </c>
+      <c r="D18" s="2" t="inlineStr">
+        <is>
+          <t>7820</t>
+        </is>
+      </c>
+      <c r="E18" s="2" t="inlineStr">
+        <is>
+          <t>7820</t>
+        </is>
+      </c>
+      <c r="F18" s="2" t="inlineStr">
+        <is>
+          <t>7820</t>
+        </is>
+      </c>
+      <c r="G18" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H18" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I18" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J18" s="2" t="inlineStr">
+        <is>
           <t>13</t>
         </is>
       </c>
-      <c r="D18" s="2" t="inlineStr">
+      <c r="K18" s="2" t="inlineStr">
         <is>
           <t>9126</t>
         </is>
       </c>
-      <c r="E18" s="2" t="inlineStr">
+      <c r="L18" s="2" t="inlineStr">
         <is>
           <t>9126</t>
         </is>
       </c>
-      <c r="F18" s="2" t="inlineStr">
+      <c r="M18" s="2" t="inlineStr">
         <is>
           <t>9126</t>
-        </is>
-      </c>
-      <c r="G18" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H18" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I18" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J18" s="2" t="inlineStr">
-        <is>
-          <t>11</t>
-        </is>
-      </c>
-      <c r="K18" s="2" t="inlineStr">
-        <is>
-          <t>7820</t>
-        </is>
-      </c>
-      <c r="L18" s="2" t="inlineStr">
-        <is>
-          <t>7820</t>
-        </is>
-      </c>
-      <c r="M18" s="2" t="inlineStr">
-        <is>
-          <t>7820</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
@@ -2437,107 +2437,107 @@
       </c>
       <c r="C19" s="2" t="inlineStr">
         <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="D19" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="E19" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="F19" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G19" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="H19" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="I19" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="J19" s="2" t="inlineStr">
+        <is>
           <t>1</t>
         </is>
       </c>
-      <c r="D19" s="2" t="inlineStr">
+      <c r="K19" s="2" t="inlineStr">
         <is>
           <t>620</t>
         </is>
       </c>
-      <c r="E19" s="2" t="inlineStr">
+      <c r="L19" s="2" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="F19" s="2" t="inlineStr">
-        <is>
-          <t>3069</t>
-        </is>
-      </c>
-      <c r="G19" s="2" t="inlineStr">
+      <c r="M19" s="2" t="inlineStr">
+        <is>
+          <t>2975</t>
+        </is>
+      </c>
+      <c r="N19" s="2" t="inlineStr">
         <is>
           <t>5,01%</t>
         </is>
       </c>
-      <c r="H19" s="2" t="inlineStr">
+      <c r="O19" s="2" t="inlineStr">
         <is>
           <t>0,0%</t>
         </is>
       </c>
-      <c r="I19" s="2" t="inlineStr">
-        <is>
-          <t>24,79%</t>
-        </is>
-      </c>
-      <c r="J19" s="2" t="inlineStr">
+      <c r="P19" s="2" t="inlineStr">
+        <is>
+          <t>24,03%</t>
+        </is>
+      </c>
+      <c r="Q19" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="R19" s="2" t="inlineStr">
+        <is>
+          <t>620</t>
+        </is>
+      </c>
+      <c r="S19" s="2" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="K19" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="L19" s="2" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="M19" s="2" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="N19" s="2" t="inlineStr">
+      <c r="T19" s="2" t="inlineStr">
+        <is>
+          <t>3136</t>
+        </is>
+      </c>
+      <c r="U19" s="2" t="inlineStr">
+        <is>
+          <t>2,68%</t>
+        </is>
+      </c>
+      <c r="V19" s="2" t="inlineStr">
         <is>
           <t>0,0%</t>
         </is>
       </c>
-      <c r="O19" s="2" t="inlineStr">
-        <is>
-          <t>—%</t>
-        </is>
-      </c>
-      <c r="P19" s="2" t="inlineStr">
-        <is>
-          <t>—%</t>
-        </is>
-      </c>
-      <c r="Q19" s="2" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="R19" s="2" t="inlineStr">
-        <is>
-          <t>620</t>
-        </is>
-      </c>
-      <c r="S19" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="T19" s="2" t="inlineStr">
-        <is>
-          <t>2501</t>
-        </is>
-      </c>
-      <c r="U19" s="2" t="inlineStr">
-        <is>
-          <t>2,68%</t>
-        </is>
-      </c>
-      <c r="V19" s="2" t="inlineStr">
-        <is>
-          <t>0,0%</t>
-        </is>
-      </c>
       <c r="W19" s="2" t="inlineStr">
         <is>
-          <t>10,82%</t>
+          <t>13,57%</t>
         </is>
       </c>
     </row>
@@ -2555,69 +2555,69 @@
       </c>
       <c r="D20" s="2" t="inlineStr">
         <is>
+          <t>10729</t>
+        </is>
+      </c>
+      <c r="E20" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="F20" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G20" s="2" t="inlineStr">
+        <is>
+          <t>100,0%</t>
+        </is>
+      </c>
+      <c r="H20" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="I20" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="J20" s="2" t="inlineStr">
+        <is>
+          <t>17</t>
+        </is>
+      </c>
+      <c r="K20" s="2" t="inlineStr">
+        <is>
           <t>11759</t>
         </is>
       </c>
-      <c r="E20" s="2" t="inlineStr">
-        <is>
-          <t>9310</t>
-        </is>
-      </c>
-      <c r="F20" s="2" t="inlineStr">
+      <c r="L20" s="2" t="inlineStr">
+        <is>
+          <t>9404</t>
+        </is>
+      </c>
+      <c r="M20" s="2" t="inlineStr">
         <is>
           <t>12379</t>
         </is>
       </c>
-      <c r="G20" s="2" t="inlineStr">
+      <c r="N20" s="2" t="inlineStr">
         <is>
           <t>94,99%</t>
         </is>
       </c>
-      <c r="H20" s="2" t="inlineStr">
-        <is>
-          <t>75,21%</t>
-        </is>
-      </c>
-      <c r="I20" s="2" t="inlineStr">
+      <c r="O20" s="2" t="inlineStr">
+        <is>
+          <t>75,97%</t>
+        </is>
+      </c>
+      <c r="P20" s="2" t="inlineStr">
         <is>
           <t>100,0%</t>
         </is>
       </c>
-      <c r="J20" s="2" t="inlineStr">
-        <is>
-          <t>17</t>
-        </is>
-      </c>
-      <c r="K20" s="2" t="inlineStr">
-        <is>
-          <t>10729</t>
-        </is>
-      </c>
-      <c r="L20" s="2" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="M20" s="2" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="N20" s="2" t="inlineStr">
-        <is>
-          <t>100,0%</t>
-        </is>
-      </c>
-      <c r="O20" s="2" t="inlineStr">
-        <is>
-          <t>—%</t>
-        </is>
-      </c>
-      <c r="P20" s="2" t="inlineStr">
-        <is>
-          <t>—%</t>
-        </is>
-      </c>
       <c r="Q20" s="2" t="inlineStr">
         <is>
           <t>34</t>
@@ -2630,7 +2630,7 @@
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>20607</t>
+          <t>19972</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
@@ -2645,7 +2645,7 @@
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>89,18%</t>
+          <t>86,43%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
@@ -2663,57 +2663,57 @@
       </c>
       <c r="C21" s="2" t="inlineStr">
         <is>
+          <t>17</t>
+        </is>
+      </c>
+      <c r="D21" s="2" t="inlineStr">
+        <is>
+          <t>10729</t>
+        </is>
+      </c>
+      <c r="E21" s="2" t="inlineStr">
+        <is>
+          <t>10729</t>
+        </is>
+      </c>
+      <c r="F21" s="2" t="inlineStr">
+        <is>
+          <t>10729</t>
+        </is>
+      </c>
+      <c r="G21" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H21" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I21" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J21" s="2" t="inlineStr">
+        <is>
           <t>18</t>
         </is>
       </c>
-      <c r="D21" s="2" t="inlineStr">
+      <c r="K21" s="2" t="inlineStr">
         <is>
           <t>12379</t>
         </is>
       </c>
-      <c r="E21" s="2" t="inlineStr">
+      <c r="L21" s="2" t="inlineStr">
         <is>
           <t>12379</t>
         </is>
       </c>
-      <c r="F21" s="2" t="inlineStr">
+      <c r="M21" s="2" t="inlineStr">
         <is>
           <t>12379</t>
-        </is>
-      </c>
-      <c r="G21" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H21" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I21" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J21" s="2" t="inlineStr">
-        <is>
-          <t>17</t>
-        </is>
-      </c>
-      <c r="K21" s="2" t="inlineStr">
-        <is>
-          <t>10729</t>
-        </is>
-      </c>
-      <c r="L21" s="2" t="inlineStr">
-        <is>
-          <t>10729</t>
-        </is>
-      </c>
-      <c r="M21" s="2" t="inlineStr">
-        <is>
-          <t>10729</t>
         </is>
       </c>
       <c r="N21" s="2" t="inlineStr">
@@ -2785,102 +2785,102 @@
       </c>
       <c r="D22" s="2" t="inlineStr">
         <is>
+          <t>725</t>
+        </is>
+      </c>
+      <c r="E22" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="F22" s="2" t="inlineStr">
+        <is>
+          <t>3633</t>
+        </is>
+      </c>
+      <c r="G22" s="2" t="inlineStr">
+        <is>
+          <t>2,73%</t>
+        </is>
+      </c>
+      <c r="H22" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="I22" s="2" t="inlineStr">
+        <is>
+          <t>13,7%</t>
+        </is>
+      </c>
+      <c r="J22" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="K22" s="2" t="inlineStr">
+        <is>
           <t>665</t>
         </is>
       </c>
-      <c r="E22" s="2" t="inlineStr">
+      <c r="L22" s="2" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="F22" s="2" t="inlineStr">
-        <is>
-          <t>3315</t>
-        </is>
-      </c>
-      <c r="G22" s="2" t="inlineStr">
+      <c r="M22" s="2" t="inlineStr">
+        <is>
+          <t>3115</t>
+        </is>
+      </c>
+      <c r="N22" s="2" t="inlineStr">
         <is>
           <t>3,1%</t>
         </is>
       </c>
-      <c r="H22" s="2" t="inlineStr">
+      <c r="O22" s="2" t="inlineStr">
         <is>
           <t>0,0%</t>
         </is>
       </c>
-      <c r="I22" s="2" t="inlineStr">
-        <is>
-          <t>15,42%</t>
-        </is>
-      </c>
-      <c r="J22" s="2" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="K22" s="2" t="inlineStr">
-        <is>
-          <t>725</t>
-        </is>
-      </c>
-      <c r="L22" s="2" t="inlineStr">
+      <c r="P22" s="2" t="inlineStr">
+        <is>
+          <t>14,49%</t>
+        </is>
+      </c>
+      <c r="Q22" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="R22" s="2" t="inlineStr">
+        <is>
+          <t>1391</t>
+        </is>
+      </c>
+      <c r="S22" s="2" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="M22" s="2" t="inlineStr">
-        <is>
-          <t>3489</t>
-        </is>
-      </c>
-      <c r="N22" s="2" t="inlineStr">
-        <is>
-          <t>2,73%</t>
-        </is>
-      </c>
-      <c r="O22" s="2" t="inlineStr">
+      <c r="T22" s="2" t="inlineStr">
+        <is>
+          <t>4898</t>
+        </is>
+      </c>
+      <c r="U22" s="2" t="inlineStr">
+        <is>
+          <t>2,9%</t>
+        </is>
+      </c>
+      <c r="V22" s="2" t="inlineStr">
         <is>
           <t>0,0%</t>
         </is>
       </c>
-      <c r="P22" s="2" t="inlineStr">
-        <is>
-          <t>13,15%</t>
-        </is>
-      </c>
-      <c r="Q22" s="2" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="R22" s="2" t="inlineStr">
-        <is>
-          <t>1391</t>
-        </is>
-      </c>
-      <c r="S22" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="T22" s="2" t="inlineStr">
-        <is>
-          <t>4591</t>
-        </is>
-      </c>
-      <c r="U22" s="2" t="inlineStr">
-        <is>
-          <t>2,9%</t>
-        </is>
-      </c>
-      <c r="V22" s="2" t="inlineStr">
-        <is>
-          <t>0,0%</t>
-        </is>
-      </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>9,56%</t>
+          <t>10,2%</t>
         </is>
       </c>
     </row>
@@ -2893,74 +2893,74 @@
       </c>
       <c r="C23" s="2" t="inlineStr">
         <is>
+          <t>37</t>
+        </is>
+      </c>
+      <c r="D23" s="2" t="inlineStr">
+        <is>
+          <t>25801</t>
+        </is>
+      </c>
+      <c r="E23" s="2" t="inlineStr">
+        <is>
+          <t>22893</t>
+        </is>
+      </c>
+      <c r="F23" s="2" t="inlineStr">
+        <is>
+          <t>26526</t>
+        </is>
+      </c>
+      <c r="G23" s="2" t="inlineStr">
+        <is>
+          <t>97,27%</t>
+        </is>
+      </c>
+      <c r="H23" s="2" t="inlineStr">
+        <is>
+          <t>86,3%</t>
+        </is>
+      </c>
+      <c r="I23" s="2" t="inlineStr">
+        <is>
+          <t>100,0%</t>
+        </is>
+      </c>
+      <c r="J23" s="2" t="inlineStr">
+        <is>
           <t>30</t>
         </is>
       </c>
-      <c r="D23" s="2" t="inlineStr">
+      <c r="K23" s="2" t="inlineStr">
         <is>
           <t>20834</t>
         </is>
       </c>
-      <c r="E23" s="2" t="inlineStr">
-        <is>
-          <t>18184</t>
-        </is>
-      </c>
-      <c r="F23" s="2" t="inlineStr">
+      <c r="L23" s="2" t="inlineStr">
+        <is>
+          <t>18384</t>
+        </is>
+      </c>
+      <c r="M23" s="2" t="inlineStr">
         <is>
           <t>21499</t>
         </is>
       </c>
-      <c r="G23" s="2" t="inlineStr">
+      <c r="N23" s="2" t="inlineStr">
         <is>
           <t>96,9%</t>
         </is>
       </c>
-      <c r="H23" s="2" t="inlineStr">
-        <is>
-          <t>84,58%</t>
-        </is>
-      </c>
-      <c r="I23" s="2" t="inlineStr">
+      <c r="O23" s="2" t="inlineStr">
+        <is>
+          <t>85,51%</t>
+        </is>
+      </c>
+      <c r="P23" s="2" t="inlineStr">
         <is>
           <t>100,0%</t>
         </is>
       </c>
-      <c r="J23" s="2" t="inlineStr">
-        <is>
-          <t>37</t>
-        </is>
-      </c>
-      <c r="K23" s="2" t="inlineStr">
-        <is>
-          <t>25801</t>
-        </is>
-      </c>
-      <c r="L23" s="2" t="inlineStr">
-        <is>
-          <t>23037</t>
-        </is>
-      </c>
-      <c r="M23" s="2" t="inlineStr">
-        <is>
-          <t>26526</t>
-        </is>
-      </c>
-      <c r="N23" s="2" t="inlineStr">
-        <is>
-          <t>97,27%</t>
-        </is>
-      </c>
-      <c r="O23" s="2" t="inlineStr">
-        <is>
-          <t>86,85%</t>
-        </is>
-      </c>
-      <c r="P23" s="2" t="inlineStr">
-        <is>
-          <t>100,0%</t>
-        </is>
-      </c>
       <c r="Q23" s="2" t="inlineStr">
         <is>
           <t>67</t>
@@ -2973,7 +2973,7 @@
       </c>
       <c r="S23" s="2" t="inlineStr">
         <is>
-          <t>43434</t>
+          <t>43127</t>
         </is>
       </c>
       <c r="T23" s="2" t="inlineStr">
@@ -2988,7 +2988,7 @@
       </c>
       <c r="V23" s="2" t="inlineStr">
         <is>
-          <t>90,44%</t>
+          <t>89,8%</t>
         </is>
       </c>
       <c r="W23" s="2" t="inlineStr">
@@ -3006,57 +3006,57 @@
       </c>
       <c r="C24" s="2" t="inlineStr">
         <is>
+          <t>38</t>
+        </is>
+      </c>
+      <c r="D24" s="2" t="inlineStr">
+        <is>
+          <t>26526</t>
+        </is>
+      </c>
+      <c r="E24" s="2" t="inlineStr">
+        <is>
+          <t>26526</t>
+        </is>
+      </c>
+      <c r="F24" s="2" t="inlineStr">
+        <is>
+          <t>26526</t>
+        </is>
+      </c>
+      <c r="G24" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H24" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I24" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J24" s="2" t="inlineStr">
+        <is>
           <t>31</t>
         </is>
       </c>
-      <c r="D24" s="2" t="inlineStr">
+      <c r="K24" s="2" t="inlineStr">
         <is>
           <t>21499</t>
         </is>
       </c>
-      <c r="E24" s="2" t="inlineStr">
+      <c r="L24" s="2" t="inlineStr">
         <is>
           <t>21499</t>
         </is>
       </c>
-      <c r="F24" s="2" t="inlineStr">
+      <c r="M24" s="2" t="inlineStr">
         <is>
           <t>21499</t>
-        </is>
-      </c>
-      <c r="G24" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H24" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I24" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J24" s="2" t="inlineStr">
-        <is>
-          <t>38</t>
-        </is>
-      </c>
-      <c r="K24" s="2" t="inlineStr">
-        <is>
-          <t>26526</t>
-        </is>
-      </c>
-      <c r="L24" s="2" t="inlineStr">
-        <is>
-          <t>26526</t>
-        </is>
-      </c>
-      <c r="M24" s="2" t="inlineStr">
-        <is>
-          <t>26526</t>
         </is>
       </c>
       <c r="N24" s="2" t="inlineStr">
@@ -3123,107 +3123,107 @@
       </c>
       <c r="C25" s="2" t="inlineStr">
         <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="D25" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="E25" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="F25" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G25" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="H25" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="I25" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="J25" s="2" t="inlineStr">
+        <is>
           <t>2</t>
         </is>
       </c>
-      <c r="D25" s="2" t="inlineStr">
+      <c r="K25" s="2" t="inlineStr">
         <is>
           <t>1102</t>
         </is>
       </c>
-      <c r="E25" s="2" t="inlineStr">
+      <c r="L25" s="2" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="F25" s="2" t="inlineStr">
-        <is>
-          <t>3486</t>
-        </is>
-      </c>
-      <c r="G25" s="2" t="inlineStr">
+      <c r="M25" s="2" t="inlineStr">
+        <is>
+          <t>3852</t>
+        </is>
+      </c>
+      <c r="N25" s="2" t="inlineStr">
         <is>
           <t>4,25%</t>
         </is>
       </c>
-      <c r="H25" s="2" t="inlineStr">
+      <c r="O25" s="2" t="inlineStr">
         <is>
           <t>0,0%</t>
         </is>
       </c>
-      <c r="I25" s="2" t="inlineStr">
-        <is>
-          <t>13,45%</t>
-        </is>
-      </c>
-      <c r="J25" s="2" t="inlineStr">
+      <c r="P25" s="2" t="inlineStr">
+        <is>
+          <t>14,86%</t>
+        </is>
+      </c>
+      <c r="Q25" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="R25" s="2" t="inlineStr">
+        <is>
+          <t>1102</t>
+        </is>
+      </c>
+      <c r="S25" s="2" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="K25" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="L25" s="2" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="M25" s="2" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="N25" s="2" t="inlineStr">
+      <c r="T25" s="2" t="inlineStr">
+        <is>
+          <t>3820</t>
+        </is>
+      </c>
+      <c r="U25" s="2" t="inlineStr">
+        <is>
+          <t>1,67%</t>
+        </is>
+      </c>
+      <c r="V25" s="2" t="inlineStr">
         <is>
           <t>0,0%</t>
         </is>
       </c>
-      <c r="O25" s="2" t="inlineStr">
-        <is>
-          <t>—%</t>
-        </is>
-      </c>
-      <c r="P25" s="2" t="inlineStr">
-        <is>
-          <t>—%</t>
-        </is>
-      </c>
-      <c r="Q25" s="2" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="R25" s="2" t="inlineStr">
-        <is>
-          <t>1102</t>
-        </is>
-      </c>
-      <c r="S25" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="T25" s="2" t="inlineStr">
-        <is>
-          <t>3671</t>
-        </is>
-      </c>
-      <c r="U25" s="2" t="inlineStr">
-        <is>
-          <t>1,67%</t>
-        </is>
-      </c>
-      <c r="V25" s="2" t="inlineStr">
-        <is>
-          <t>0,0%</t>
-        </is>
-      </c>
       <c r="W25" s="2" t="inlineStr">
         <is>
-          <t>5,58%</t>
+          <t>5,81%</t>
         </is>
       </c>
     </row>
@@ -3236,74 +3236,74 @@
       </c>
       <c r="C26" s="2" t="inlineStr">
         <is>
+          <t>62</t>
+        </is>
+      </c>
+      <c r="D26" s="2" t="inlineStr">
+        <is>
+          <t>39867</t>
+        </is>
+      </c>
+      <c r="E26" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="F26" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G26" s="2" t="inlineStr">
+        <is>
+          <t>100,0%</t>
+        </is>
+      </c>
+      <c r="H26" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="I26" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="J26" s="2" t="inlineStr">
+        <is>
           <t>40</t>
         </is>
       </c>
-      <c r="D26" s="2" t="inlineStr">
+      <c r="K26" s="2" t="inlineStr">
         <is>
           <t>24822</t>
         </is>
       </c>
-      <c r="E26" s="2" t="inlineStr">
-        <is>
-          <t>22438</t>
-        </is>
-      </c>
-      <c r="F26" s="2" t="inlineStr">
+      <c r="L26" s="2" t="inlineStr">
+        <is>
+          <t>22072</t>
+        </is>
+      </c>
+      <c r="M26" s="2" t="inlineStr">
         <is>
           <t>25924</t>
         </is>
       </c>
-      <c r="G26" s="2" t="inlineStr">
+      <c r="N26" s="2" t="inlineStr">
         <is>
           <t>95,75%</t>
         </is>
       </c>
-      <c r="H26" s="2" t="inlineStr">
-        <is>
-          <t>86,55%</t>
-        </is>
-      </c>
-      <c r="I26" s="2" t="inlineStr">
+      <c r="O26" s="2" t="inlineStr">
+        <is>
+          <t>85,14%</t>
+        </is>
+      </c>
+      <c r="P26" s="2" t="inlineStr">
         <is>
           <t>100,0%</t>
         </is>
       </c>
-      <c r="J26" s="2" t="inlineStr">
-        <is>
-          <t>62</t>
-        </is>
-      </c>
-      <c r="K26" s="2" t="inlineStr">
-        <is>
-          <t>39867</t>
-        </is>
-      </c>
-      <c r="L26" s="2" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="M26" s="2" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="N26" s="2" t="inlineStr">
-        <is>
-          <t>100,0%</t>
-        </is>
-      </c>
-      <c r="O26" s="2" t="inlineStr">
-        <is>
-          <t>—%</t>
-        </is>
-      </c>
-      <c r="P26" s="2" t="inlineStr">
-        <is>
-          <t>—%</t>
-        </is>
-      </c>
       <c r="Q26" s="2" t="inlineStr">
         <is>
           <t>102</t>
@@ -3316,7 +3316,7 @@
       </c>
       <c r="S26" s="2" t="inlineStr">
         <is>
-          <t>62119</t>
+          <t>61970</t>
         </is>
       </c>
       <c r="T26" s="2" t="inlineStr">
@@ -3331,7 +3331,7 @@
       </c>
       <c r="V26" s="2" t="inlineStr">
         <is>
-          <t>94,42%</t>
+          <t>94,19%</t>
         </is>
       </c>
       <c r="W26" s="2" t="inlineStr">
@@ -3349,57 +3349,57 @@
       </c>
       <c r="C27" s="2" t="inlineStr">
         <is>
+          <t>62</t>
+        </is>
+      </c>
+      <c r="D27" s="2" t="inlineStr">
+        <is>
+          <t>39867</t>
+        </is>
+      </c>
+      <c r="E27" s="2" t="inlineStr">
+        <is>
+          <t>39867</t>
+        </is>
+      </c>
+      <c r="F27" s="2" t="inlineStr">
+        <is>
+          <t>39867</t>
+        </is>
+      </c>
+      <c r="G27" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H27" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I27" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J27" s="2" t="inlineStr">
+        <is>
           <t>42</t>
         </is>
       </c>
-      <c r="D27" s="2" t="inlineStr">
+      <c r="K27" s="2" t="inlineStr">
         <is>
           <t>25924</t>
         </is>
       </c>
-      <c r="E27" s="2" t="inlineStr">
+      <c r="L27" s="2" t="inlineStr">
         <is>
           <t>25924</t>
         </is>
       </c>
-      <c r="F27" s="2" t="inlineStr">
+      <c r="M27" s="2" t="inlineStr">
         <is>
           <t>25924</t>
-        </is>
-      </c>
-      <c r="G27" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H27" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I27" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J27" s="2" t="inlineStr">
-        <is>
-          <t>62</t>
-        </is>
-      </c>
-      <c r="K27" s="2" t="inlineStr">
-        <is>
-          <t>39867</t>
-        </is>
-      </c>
-      <c r="L27" s="2" t="inlineStr">
-        <is>
-          <t>39867</t>
-        </is>
-      </c>
-      <c r="M27" s="2" t="inlineStr">
-        <is>
-          <t>39867</t>
         </is>
       </c>
       <c r="N27" s="2" t="inlineStr">
@@ -3466,72 +3466,72 @@
       </c>
       <c r="C28" s="2" t="inlineStr">
         <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="D28" s="2" t="inlineStr">
+        <is>
+          <t>2719</t>
+        </is>
+      </c>
+      <c r="E28" s="2" t="inlineStr">
+        <is>
+          <t>669</t>
+        </is>
+      </c>
+      <c r="F28" s="2" t="inlineStr">
+        <is>
+          <t>6504</t>
+        </is>
+      </c>
+      <c r="G28" s="2" t="inlineStr">
+        <is>
+          <t>1,89%</t>
+        </is>
+      </c>
+      <c r="H28" s="2" t="inlineStr">
+        <is>
+          <t>0,46%</t>
+        </is>
+      </c>
+      <c r="I28" s="2" t="inlineStr">
+        <is>
+          <t>4,52%</t>
+        </is>
+      </c>
+      <c r="J28" s="2" t="inlineStr">
+        <is>
           <t>12</t>
         </is>
       </c>
-      <c r="D28" s="2" t="inlineStr">
+      <c r="K28" s="2" t="inlineStr">
         <is>
           <t>6797</t>
         </is>
       </c>
-      <c r="E28" s="2" t="inlineStr">
-        <is>
-          <t>3573</t>
-        </is>
-      </c>
-      <c r="F28" s="2" t="inlineStr">
-        <is>
-          <t>11072</t>
-        </is>
-      </c>
-      <c r="G28" s="2" t="inlineStr">
+      <c r="L28" s="2" t="inlineStr">
+        <is>
+          <t>3809</t>
+        </is>
+      </c>
+      <c r="M28" s="2" t="inlineStr">
+        <is>
+          <t>11888</t>
+        </is>
+      </c>
+      <c r="N28" s="2" t="inlineStr">
         <is>
           <t>5,42%</t>
         </is>
       </c>
-      <c r="H28" s="2" t="inlineStr">
-        <is>
-          <t>2,85%</t>
-        </is>
-      </c>
-      <c r="I28" s="2" t="inlineStr">
-        <is>
-          <t>8,84%</t>
-        </is>
-      </c>
-      <c r="J28" s="2" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
-      </c>
-      <c r="K28" s="2" t="inlineStr">
-        <is>
-          <t>2719</t>
-        </is>
-      </c>
-      <c r="L28" s="2" t="inlineStr">
-        <is>
-          <t>683</t>
-        </is>
-      </c>
-      <c r="M28" s="2" t="inlineStr">
-        <is>
-          <t>6916</t>
-        </is>
-      </c>
-      <c r="N28" s="2" t="inlineStr">
-        <is>
-          <t>1,89%</t>
-        </is>
-      </c>
       <c r="O28" s="2" t="inlineStr">
         <is>
-          <t>0,47%</t>
+          <t>3,04%</t>
         </is>
       </c>
       <c r="P28" s="2" t="inlineStr">
         <is>
-          <t>4,81%</t>
+          <t>9,49%</t>
         </is>
       </c>
       <c r="Q28" s="2" t="inlineStr">
@@ -3546,12 +3546,12 @@
       </c>
       <c r="S28" s="2" t="inlineStr">
         <is>
-          <t>5721</t>
+          <t>5723</t>
         </is>
       </c>
       <c r="T28" s="2" t="inlineStr">
         <is>
-          <t>14906</t>
+          <t>15037</t>
         </is>
       </c>
       <c r="U28" s="2" t="inlineStr">
@@ -3566,7 +3566,7 @@
       </c>
       <c r="W28" s="2" t="inlineStr">
         <is>
-          <t>5,54%</t>
+          <t>5,59%</t>
         </is>
       </c>
     </row>
@@ -3579,72 +3579,72 @@
       </c>
       <c r="C29" s="2" t="inlineStr">
         <is>
+          <t>211</t>
+        </is>
+      </c>
+      <c r="D29" s="2" t="inlineStr">
+        <is>
+          <t>141200</t>
+        </is>
+      </c>
+      <c r="E29" s="2" t="inlineStr">
+        <is>
+          <t>137415</t>
+        </is>
+      </c>
+      <c r="F29" s="2" t="inlineStr">
+        <is>
+          <t>143250</t>
+        </is>
+      </c>
+      <c r="G29" s="2" t="inlineStr">
+        <is>
+          <t>98,11%</t>
+        </is>
+      </c>
+      <c r="H29" s="2" t="inlineStr">
+        <is>
+          <t>95,48%</t>
+        </is>
+      </c>
+      <c r="I29" s="2" t="inlineStr">
+        <is>
+          <t>99,54%</t>
+        </is>
+      </c>
+      <c r="J29" s="2" t="inlineStr">
+        <is>
           <t>178</t>
         </is>
       </c>
-      <c r="D29" s="2" t="inlineStr">
+      <c r="K29" s="2" t="inlineStr">
         <is>
           <t>118508</t>
         </is>
       </c>
-      <c r="E29" s="2" t="inlineStr">
-        <is>
-          <t>114233</t>
-        </is>
-      </c>
-      <c r="F29" s="2" t="inlineStr">
-        <is>
-          <t>121732</t>
-        </is>
-      </c>
-      <c r="G29" s="2" t="inlineStr">
+      <c r="L29" s="2" t="inlineStr">
+        <is>
+          <t>113417</t>
+        </is>
+      </c>
+      <c r="M29" s="2" t="inlineStr">
+        <is>
+          <t>121496</t>
+        </is>
+      </c>
+      <c r="N29" s="2" t="inlineStr">
         <is>
           <t>94,58%</t>
         </is>
       </c>
-      <c r="H29" s="2" t="inlineStr">
-        <is>
-          <t>91,16%</t>
-        </is>
-      </c>
-      <c r="I29" s="2" t="inlineStr">
-        <is>
-          <t>97,15%</t>
-        </is>
-      </c>
-      <c r="J29" s="2" t="inlineStr">
-        <is>
-          <t>211</t>
-        </is>
-      </c>
-      <c r="K29" s="2" t="inlineStr">
-        <is>
-          <t>141200</t>
-        </is>
-      </c>
-      <c r="L29" s="2" t="inlineStr">
-        <is>
-          <t>137003</t>
-        </is>
-      </c>
-      <c r="M29" s="2" t="inlineStr">
-        <is>
-          <t>143236</t>
-        </is>
-      </c>
-      <c r="N29" s="2" t="inlineStr">
-        <is>
-          <t>98,11%</t>
-        </is>
-      </c>
       <c r="O29" s="2" t="inlineStr">
         <is>
-          <t>95,19%</t>
+          <t>90,51%</t>
         </is>
       </c>
       <c r="P29" s="2" t="inlineStr">
         <is>
-          <t>99,53%</t>
+          <t>96,96%</t>
         </is>
       </c>
       <c r="Q29" s="2" t="inlineStr">
@@ -3659,12 +3659,12 @@
       </c>
       <c r="S29" s="2" t="inlineStr">
         <is>
-          <t>254318</t>
+          <t>254187</t>
         </is>
       </c>
       <c r="T29" s="2" t="inlineStr">
         <is>
-          <t>263503</t>
+          <t>263501</t>
         </is>
       </c>
       <c r="U29" s="2" t="inlineStr">
@@ -3674,7 +3674,7 @@
       </c>
       <c r="V29" s="2" t="inlineStr">
         <is>
-          <t>94,46%</t>
+          <t>94,41%</t>
         </is>
       </c>
       <c r="W29" s="2" t="inlineStr">
@@ -3692,57 +3692,57 @@
       </c>
       <c r="C30" s="2" t="inlineStr">
         <is>
+          <t>215</t>
+        </is>
+      </c>
+      <c r="D30" s="2" t="inlineStr">
+        <is>
+          <t>143919</t>
+        </is>
+      </c>
+      <c r="E30" s="2" t="inlineStr">
+        <is>
+          <t>143919</t>
+        </is>
+      </c>
+      <c r="F30" s="2" t="inlineStr">
+        <is>
+          <t>143919</t>
+        </is>
+      </c>
+      <c r="G30" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H30" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I30" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J30" s="2" t="inlineStr">
+        <is>
           <t>190</t>
         </is>
       </c>
-      <c r="D30" s="2" t="inlineStr">
+      <c r="K30" s="2" t="inlineStr">
         <is>
           <t>125305</t>
         </is>
       </c>
-      <c r="E30" s="2" t="inlineStr">
+      <c r="L30" s="2" t="inlineStr">
         <is>
           <t>125305</t>
         </is>
       </c>
-      <c r="F30" s="2" t="inlineStr">
+      <c r="M30" s="2" t="inlineStr">
         <is>
           <t>125305</t>
-        </is>
-      </c>
-      <c r="G30" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H30" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I30" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J30" s="2" t="inlineStr">
-        <is>
-          <t>215</t>
-        </is>
-      </c>
-      <c r="K30" s="2" t="inlineStr">
-        <is>
-          <t>143919</t>
-        </is>
-      </c>
-      <c r="L30" s="2" t="inlineStr">
-        <is>
-          <t>143919</t>
-        </is>
-      </c>
-      <c r="M30" s="2" t="inlineStr">
-        <is>
-          <t>143919</t>
         </is>
       </c>
       <c r="N30" s="2" t="inlineStr">
@@ -3866,7 +3866,7 @@
       <c r="B1" s="2" t="n"/>
       <c r="C1" s="3" t="inlineStr">
         <is>
-          <t>Niña</t>
+          <t>Niño</t>
         </is>
       </c>
       <c r="D1" s="3" t="n"/>
@@ -3877,7 +3877,7 @@
       <c r="I1" s="3" t="n"/>
       <c r="J1" s="3" t="inlineStr">
         <is>
-          <t>Niño</t>
+          <t>Niña</t>
         </is>
       </c>
       <c r="K1" s="3" t="n"/>
@@ -4050,102 +4050,102 @@
       </c>
       <c r="D4" s="2" t="inlineStr">
         <is>
+          <t>887</t>
+        </is>
+      </c>
+      <c r="E4" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="F4" s="2" t="inlineStr">
+        <is>
+          <t>4465</t>
+        </is>
+      </c>
+      <c r="G4" s="2" t="inlineStr">
+        <is>
+          <t>3,61%</t>
+        </is>
+      </c>
+      <c r="H4" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="I4" s="2" t="inlineStr">
+        <is>
+          <t>18,16%</t>
+        </is>
+      </c>
+      <c r="J4" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="K4" s="2" t="inlineStr">
+        <is>
           <t>498</t>
         </is>
       </c>
-      <c r="E4" s="2" t="inlineStr">
+      <c r="L4" s="2" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="F4" s="2" t="inlineStr">
-        <is>
-          <t>2696</t>
-        </is>
-      </c>
-      <c r="G4" s="2" t="inlineStr">
+      <c r="M4" s="2" t="inlineStr">
+        <is>
+          <t>2424</t>
+        </is>
+      </c>
+      <c r="N4" s="2" t="inlineStr">
         <is>
           <t>2,61%</t>
         </is>
       </c>
-      <c r="H4" s="2" t="inlineStr">
+      <c r="O4" s="2" t="inlineStr">
         <is>
           <t>0,0%</t>
         </is>
       </c>
-      <c r="I4" s="2" t="inlineStr">
-        <is>
-          <t>14,15%</t>
-        </is>
-      </c>
-      <c r="J4" s="2" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="K4" s="2" t="inlineStr">
-        <is>
-          <t>887</t>
-        </is>
-      </c>
-      <c r="L4" s="2" t="inlineStr">
+      <c r="P4" s="2" t="inlineStr">
+        <is>
+          <t>12,72%</t>
+        </is>
+      </c>
+      <c r="Q4" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="R4" s="2" t="inlineStr">
+        <is>
+          <t>1386</t>
+        </is>
+      </c>
+      <c r="S4" s="2" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="M4" s="2" t="inlineStr">
-        <is>
-          <t>3863</t>
-        </is>
-      </c>
-      <c r="N4" s="2" t="inlineStr">
-        <is>
-          <t>3,61%</t>
-        </is>
-      </c>
-      <c r="O4" s="2" t="inlineStr">
+      <c r="T4" s="2" t="inlineStr">
+        <is>
+          <t>5480</t>
+        </is>
+      </c>
+      <c r="U4" s="2" t="inlineStr">
+        <is>
+          <t>3,18%</t>
+        </is>
+      </c>
+      <c r="V4" s="2" t="inlineStr">
         <is>
           <t>0,0%</t>
         </is>
       </c>
-      <c r="P4" s="2" t="inlineStr">
-        <is>
-          <t>15,72%</t>
-        </is>
-      </c>
-      <c r="Q4" s="2" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="R4" s="2" t="inlineStr">
-        <is>
-          <t>1386</t>
-        </is>
-      </c>
-      <c r="S4" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="T4" s="2" t="inlineStr">
-        <is>
-          <t>4638</t>
-        </is>
-      </c>
-      <c r="U4" s="2" t="inlineStr">
-        <is>
-          <t>3,18%</t>
-        </is>
-      </c>
-      <c r="V4" s="2" t="inlineStr">
-        <is>
-          <t>0,0%</t>
-        </is>
-      </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>10,63%</t>
+          <t>12,56%</t>
         </is>
       </c>
     </row>
@@ -4158,74 +4158,74 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
+          <t>32</t>
+        </is>
+      </c>
+      <c r="D5" s="2" t="inlineStr">
+        <is>
+          <t>23696</t>
+        </is>
+      </c>
+      <c r="E5" s="2" t="inlineStr">
+        <is>
+          <t>20118</t>
+        </is>
+      </c>
+      <c r="F5" s="2" t="inlineStr">
+        <is>
+          <t>24583</t>
+        </is>
+      </c>
+      <c r="G5" s="2" t="inlineStr">
+        <is>
+          <t>96,39%</t>
+        </is>
+      </c>
+      <c r="H5" s="2" t="inlineStr">
+        <is>
+          <t>81,84%</t>
+        </is>
+      </c>
+      <c r="I5" s="2" t="inlineStr">
+        <is>
+          <t>100,0%</t>
+        </is>
+      </c>
+      <c r="J5" s="2" t="inlineStr">
+        <is>
           <t>27</t>
         </is>
       </c>
-      <c r="D5" s="2" t="inlineStr">
+      <c r="K5" s="2" t="inlineStr">
         <is>
           <t>18562</t>
         </is>
       </c>
-      <c r="E5" s="2" t="inlineStr">
-        <is>
-          <t>16364</t>
-        </is>
-      </c>
-      <c r="F5" s="2" t="inlineStr">
+      <c r="L5" s="2" t="inlineStr">
+        <is>
+          <t>16636</t>
+        </is>
+      </c>
+      <c r="M5" s="2" t="inlineStr">
         <is>
           <t>19060</t>
         </is>
       </c>
-      <c r="G5" s="2" t="inlineStr">
+      <c r="N5" s="2" t="inlineStr">
         <is>
           <t>97,39%</t>
         </is>
       </c>
-      <c r="H5" s="2" t="inlineStr">
-        <is>
-          <t>85,85%</t>
-        </is>
-      </c>
-      <c r="I5" s="2" t="inlineStr">
+      <c r="O5" s="2" t="inlineStr">
+        <is>
+          <t>87,28%</t>
+        </is>
+      </c>
+      <c r="P5" s="2" t="inlineStr">
         <is>
           <t>100,0%</t>
         </is>
       </c>
-      <c r="J5" s="2" t="inlineStr">
-        <is>
-          <t>32</t>
-        </is>
-      </c>
-      <c r="K5" s="2" t="inlineStr">
-        <is>
-          <t>23696</t>
-        </is>
-      </c>
-      <c r="L5" s="2" t="inlineStr">
-        <is>
-          <t>20720</t>
-        </is>
-      </c>
-      <c r="M5" s="2" t="inlineStr">
-        <is>
-          <t>24583</t>
-        </is>
-      </c>
-      <c r="N5" s="2" t="inlineStr">
-        <is>
-          <t>96,39%</t>
-        </is>
-      </c>
-      <c r="O5" s="2" t="inlineStr">
-        <is>
-          <t>84,28%</t>
-        </is>
-      </c>
-      <c r="P5" s="2" t="inlineStr">
-        <is>
-          <t>100,0%</t>
-        </is>
-      </c>
       <c r="Q5" s="2" t="inlineStr">
         <is>
           <t>59</t>
@@ -4238,7 +4238,7 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>39006</t>
+          <t>38164</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
@@ -4253,7 +4253,7 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>89,37%</t>
+          <t>87,44%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
@@ -4271,57 +4271,57 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
+          <t>33</t>
+        </is>
+      </c>
+      <c r="D6" s="2" t="inlineStr">
+        <is>
+          <t>24583</t>
+        </is>
+      </c>
+      <c r="E6" s="2" t="inlineStr">
+        <is>
+          <t>24583</t>
+        </is>
+      </c>
+      <c r="F6" s="2" t="inlineStr">
+        <is>
+          <t>24583</t>
+        </is>
+      </c>
+      <c r="G6" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H6" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I6" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J6" s="2" t="inlineStr">
+        <is>
           <t>28</t>
         </is>
       </c>
-      <c r="D6" s="2" t="inlineStr">
+      <c r="K6" s="2" t="inlineStr">
         <is>
           <t>19060</t>
         </is>
       </c>
-      <c r="E6" s="2" t="inlineStr">
+      <c r="L6" s="2" t="inlineStr">
         <is>
           <t>19060</t>
         </is>
       </c>
-      <c r="F6" s="2" t="inlineStr">
+      <c r="M6" s="2" t="inlineStr">
         <is>
           <t>19060</t>
-        </is>
-      </c>
-      <c r="G6" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H6" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I6" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J6" s="2" t="inlineStr">
-        <is>
-          <t>33</t>
-        </is>
-      </c>
-      <c r="K6" s="2" t="inlineStr">
-        <is>
-          <t>24583</t>
-        </is>
-      </c>
-      <c r="L6" s="2" t="inlineStr">
-        <is>
-          <t>24583</t>
-        </is>
-      </c>
-      <c r="M6" s="2" t="inlineStr">
-        <is>
-          <t>24583</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
@@ -4388,107 +4388,107 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="D7" s="2" t="inlineStr">
+        <is>
+          <t>607</t>
+        </is>
+      </c>
+      <c r="E7" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="F7" s="2" t="inlineStr">
+        <is>
+          <t>3063</t>
+        </is>
+      </c>
+      <c r="G7" s="2" t="inlineStr">
+        <is>
+          <t>1,66%</t>
+        </is>
+      </c>
+      <c r="H7" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="I7" s="2" t="inlineStr">
+        <is>
+          <t>8,35%</t>
+        </is>
+      </c>
+      <c r="J7" s="2" t="inlineStr">
+        <is>
           <t>2</t>
         </is>
       </c>
-      <c r="D7" s="2" t="inlineStr">
+      <c r="K7" s="2" t="inlineStr">
         <is>
           <t>1272</t>
         </is>
       </c>
-      <c r="E7" s="2" t="inlineStr">
+      <c r="L7" s="2" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="F7" s="2" t="inlineStr">
-        <is>
-          <t>3886</t>
-        </is>
-      </c>
-      <c r="G7" s="2" t="inlineStr">
+      <c r="M7" s="2" t="inlineStr">
+        <is>
+          <t>4466</t>
+        </is>
+      </c>
+      <c r="N7" s="2" t="inlineStr">
         <is>
           <t>3,86%</t>
         </is>
       </c>
-      <c r="H7" s="2" t="inlineStr">
+      <c r="O7" s="2" t="inlineStr">
         <is>
           <t>0,0%</t>
         </is>
       </c>
-      <c r="I7" s="2" t="inlineStr">
-        <is>
-          <t>11,79%</t>
-        </is>
-      </c>
-      <c r="J7" s="2" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="K7" s="2" t="inlineStr">
-        <is>
-          <t>607</t>
-        </is>
-      </c>
-      <c r="L7" s="2" t="inlineStr">
+      <c r="P7" s="2" t="inlineStr">
+        <is>
+          <t>13,55%</t>
+        </is>
+      </c>
+      <c r="Q7" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="R7" s="2" t="inlineStr">
+        <is>
+          <t>1879</t>
+        </is>
+      </c>
+      <c r="S7" s="2" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="M7" s="2" t="inlineStr">
-        <is>
-          <t>3155</t>
-        </is>
-      </c>
-      <c r="N7" s="2" t="inlineStr">
-        <is>
-          <t>1,66%</t>
-        </is>
-      </c>
-      <c r="O7" s="2" t="inlineStr">
+      <c r="T7" s="2" t="inlineStr">
+        <is>
+          <t>4970</t>
+        </is>
+      </c>
+      <c r="U7" s="2" t="inlineStr">
+        <is>
+          <t>2,7%</t>
+        </is>
+      </c>
+      <c r="V7" s="2" t="inlineStr">
         <is>
           <t>0,0%</t>
         </is>
       </c>
-      <c r="P7" s="2" t="inlineStr">
-        <is>
-          <t>8,61%</t>
-        </is>
-      </c>
-      <c r="Q7" s="2" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
-      <c r="R7" s="2" t="inlineStr">
-        <is>
-          <t>1879</t>
-        </is>
-      </c>
-      <c r="S7" s="2" t="inlineStr">
-        <is>
-          <t>596</t>
-        </is>
-      </c>
-      <c r="T7" s="2" t="inlineStr">
-        <is>
-          <t>4848</t>
-        </is>
-      </c>
-      <c r="U7" s="2" t="inlineStr">
-        <is>
-          <t>2,7%</t>
-        </is>
-      </c>
-      <c r="V7" s="2" t="inlineStr">
-        <is>
-          <t>0,86%</t>
-        </is>
-      </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>6,96%</t>
+          <t>7,14%</t>
         </is>
       </c>
     </row>
@@ -4501,107 +4501,107 @@
       </c>
       <c r="C8" s="2" t="inlineStr">
         <is>
+          <t>54</t>
+        </is>
+      </c>
+      <c r="D8" s="2" t="inlineStr">
+        <is>
+          <t>36059</t>
+        </is>
+      </c>
+      <c r="E8" s="2" t="inlineStr">
+        <is>
+          <t>33603</t>
+        </is>
+      </c>
+      <c r="F8" s="2" t="inlineStr">
+        <is>
+          <t>36666</t>
+        </is>
+      </c>
+      <c r="G8" s="2" t="inlineStr">
+        <is>
+          <t>98,34%</t>
+        </is>
+      </c>
+      <c r="H8" s="2" t="inlineStr">
+        <is>
+          <t>91,65%</t>
+        </is>
+      </c>
+      <c r="I8" s="2" t="inlineStr">
+        <is>
+          <t>100,0%</t>
+        </is>
+      </c>
+      <c r="J8" s="2" t="inlineStr">
+        <is>
           <t>47</t>
         </is>
       </c>
-      <c r="D8" s="2" t="inlineStr">
+      <c r="K8" s="2" t="inlineStr">
         <is>
           <t>31675</t>
         </is>
       </c>
-      <c r="E8" s="2" t="inlineStr">
-        <is>
-          <t>29061</t>
-        </is>
-      </c>
-      <c r="F8" s="2" t="inlineStr">
+      <c r="L8" s="2" t="inlineStr">
+        <is>
+          <t>28481</t>
+        </is>
+      </c>
+      <c r="M8" s="2" t="inlineStr">
         <is>
           <t>32947</t>
         </is>
       </c>
-      <c r="G8" s="2" t="inlineStr">
+      <c r="N8" s="2" t="inlineStr">
         <is>
           <t>96,14%</t>
         </is>
       </c>
-      <c r="H8" s="2" t="inlineStr">
-        <is>
-          <t>88,21%</t>
-        </is>
-      </c>
-      <c r="I8" s="2" t="inlineStr">
+      <c r="O8" s="2" t="inlineStr">
+        <is>
+          <t>86,45%</t>
+        </is>
+      </c>
+      <c r="P8" s="2" t="inlineStr">
         <is>
           <t>100,0%</t>
         </is>
       </c>
-      <c r="J8" s="2" t="inlineStr">
-        <is>
-          <t>54</t>
-        </is>
-      </c>
-      <c r="K8" s="2" t="inlineStr">
-        <is>
-          <t>36059</t>
-        </is>
-      </c>
-      <c r="L8" s="2" t="inlineStr">
-        <is>
-          <t>33511</t>
-        </is>
-      </c>
-      <c r="M8" s="2" t="inlineStr">
-        <is>
-          <t>36666</t>
-        </is>
-      </c>
-      <c r="N8" s="2" t="inlineStr">
-        <is>
-          <t>98,34%</t>
-        </is>
-      </c>
-      <c r="O8" s="2" t="inlineStr">
-        <is>
-          <t>91,39%</t>
-        </is>
-      </c>
-      <c r="P8" s="2" t="inlineStr">
+      <c r="Q8" s="2" t="inlineStr">
+        <is>
+          <t>101</t>
+        </is>
+      </c>
+      <c r="R8" s="2" t="inlineStr">
+        <is>
+          <t>67734</t>
+        </is>
+      </c>
+      <c r="S8" s="2" t="inlineStr">
+        <is>
+          <t>64643</t>
+        </is>
+      </c>
+      <c r="T8" s="2" t="inlineStr">
+        <is>
+          <t>69613</t>
+        </is>
+      </c>
+      <c r="U8" s="2" t="inlineStr">
+        <is>
+          <t>97,3%</t>
+        </is>
+      </c>
+      <c r="V8" s="2" t="inlineStr">
+        <is>
+          <t>92,86%</t>
+        </is>
+      </c>
+      <c r="W8" s="2" t="inlineStr">
         <is>
           <t>100,0%</t>
-        </is>
-      </c>
-      <c r="Q8" s="2" t="inlineStr">
-        <is>
-          <t>101</t>
-        </is>
-      </c>
-      <c r="R8" s="2" t="inlineStr">
-        <is>
-          <t>67734</t>
-        </is>
-      </c>
-      <c r="S8" s="2" t="inlineStr">
-        <is>
-          <t>64765</t>
-        </is>
-      </c>
-      <c r="T8" s="2" t="inlineStr">
-        <is>
-          <t>69017</t>
-        </is>
-      </c>
-      <c r="U8" s="2" t="inlineStr">
-        <is>
-          <t>97,3%</t>
-        </is>
-      </c>
-      <c r="V8" s="2" t="inlineStr">
-        <is>
-          <t>93,04%</t>
-        </is>
-      </c>
-      <c r="W8" s="2" t="inlineStr">
-        <is>
-          <t>99,14%</t>
         </is>
       </c>
     </row>
@@ -4614,57 +4614,57 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
+          <t>55</t>
+        </is>
+      </c>
+      <c r="D9" s="2" t="inlineStr">
+        <is>
+          <t>36666</t>
+        </is>
+      </c>
+      <c r="E9" s="2" t="inlineStr">
+        <is>
+          <t>36666</t>
+        </is>
+      </c>
+      <c r="F9" s="2" t="inlineStr">
+        <is>
+          <t>36666</t>
+        </is>
+      </c>
+      <c r="G9" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H9" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I9" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J9" s="2" t="inlineStr">
+        <is>
           <t>49</t>
         </is>
       </c>
-      <c r="D9" s="2" t="inlineStr">
+      <c r="K9" s="2" t="inlineStr">
         <is>
           <t>32947</t>
         </is>
       </c>
-      <c r="E9" s="2" t="inlineStr">
+      <c r="L9" s="2" t="inlineStr">
         <is>
           <t>32947</t>
         </is>
       </c>
-      <c r="F9" s="2" t="inlineStr">
+      <c r="M9" s="2" t="inlineStr">
         <is>
           <t>32947</t>
-        </is>
-      </c>
-      <c r="G9" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H9" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I9" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J9" s="2" t="inlineStr">
-        <is>
-          <t>55</t>
-        </is>
-      </c>
-      <c r="K9" s="2" t="inlineStr">
-        <is>
-          <t>36666</t>
-        </is>
-      </c>
-      <c r="L9" s="2" t="inlineStr">
-        <is>
-          <t>36666</t>
-        </is>
-      </c>
-      <c r="M9" s="2" t="inlineStr">
-        <is>
-          <t>36666</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
@@ -4844,47 +4844,47 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
+          <t>33</t>
+        </is>
+      </c>
+      <c r="D11" s="2" t="inlineStr">
+        <is>
+          <t>23658</t>
+        </is>
+      </c>
+      <c r="E11" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="F11" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G11" s="2" t="inlineStr">
+        <is>
+          <t>100,0%</t>
+        </is>
+      </c>
+      <c r="H11" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="I11" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="J11" s="2" t="inlineStr">
+        <is>
           <t>27</t>
         </is>
       </c>
-      <c r="D11" s="2" t="inlineStr">
+      <c r="K11" s="2" t="inlineStr">
         <is>
           <t>19276</t>
-        </is>
-      </c>
-      <c r="E11" s="2" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="F11" s="2" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="G11" s="2" t="inlineStr">
-        <is>
-          <t>100,0%</t>
-        </is>
-      </c>
-      <c r="H11" s="2" t="inlineStr">
-        <is>
-          <t>—%</t>
-        </is>
-      </c>
-      <c r="I11" s="2" t="inlineStr">
-        <is>
-          <t>—%</t>
-        </is>
-      </c>
-      <c r="J11" s="2" t="inlineStr">
-        <is>
-          <t>33</t>
-        </is>
-      </c>
-      <c r="K11" s="2" t="inlineStr">
-        <is>
-          <t>23658</t>
         </is>
       </c>
       <c r="L11" s="2" t="inlineStr">
@@ -4957,57 +4957,57 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
+          <t>33</t>
+        </is>
+      </c>
+      <c r="D12" s="2" t="inlineStr">
+        <is>
+          <t>23658</t>
+        </is>
+      </c>
+      <c r="E12" s="2" t="inlineStr">
+        <is>
+          <t>23658</t>
+        </is>
+      </c>
+      <c r="F12" s="2" t="inlineStr">
+        <is>
+          <t>23658</t>
+        </is>
+      </c>
+      <c r="G12" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H12" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I12" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J12" s="2" t="inlineStr">
+        <is>
           <t>27</t>
         </is>
       </c>
-      <c r="D12" s="2" t="inlineStr">
+      <c r="K12" s="2" t="inlineStr">
         <is>
           <t>19276</t>
         </is>
       </c>
-      <c r="E12" s="2" t="inlineStr">
+      <c r="L12" s="2" t="inlineStr">
         <is>
           <t>19276</t>
         </is>
       </c>
-      <c r="F12" s="2" t="inlineStr">
+      <c r="M12" s="2" t="inlineStr">
         <is>
           <t>19276</t>
-        </is>
-      </c>
-      <c r="G12" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H12" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I12" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J12" s="2" t="inlineStr">
-        <is>
-          <t>33</t>
-        </is>
-      </c>
-      <c r="K12" s="2" t="inlineStr">
-        <is>
-          <t>23658</t>
-        </is>
-      </c>
-      <c r="L12" s="2" t="inlineStr">
-        <is>
-          <t>23658</t>
-        </is>
-      </c>
-      <c r="M12" s="2" t="inlineStr">
-        <is>
-          <t>23658</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
@@ -5187,47 +5187,47 @@
       </c>
       <c r="C14" s="2" t="inlineStr">
         <is>
+          <t>23</t>
+        </is>
+      </c>
+      <c r="D14" s="2" t="inlineStr">
+        <is>
+          <t>16750</t>
+        </is>
+      </c>
+      <c r="E14" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="F14" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G14" s="2" t="inlineStr">
+        <is>
+          <t>100,0%</t>
+        </is>
+      </c>
+      <c r="H14" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="I14" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="J14" s="2" t="inlineStr">
+        <is>
           <t>36</t>
         </is>
       </c>
-      <c r="D14" s="2" t="inlineStr">
+      <c r="K14" s="2" t="inlineStr">
         <is>
           <t>24892</t>
-        </is>
-      </c>
-      <c r="E14" s="2" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="F14" s="2" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="G14" s="2" t="inlineStr">
-        <is>
-          <t>100,0%</t>
-        </is>
-      </c>
-      <c r="H14" s="2" t="inlineStr">
-        <is>
-          <t>—%</t>
-        </is>
-      </c>
-      <c r="I14" s="2" t="inlineStr">
-        <is>
-          <t>—%</t>
-        </is>
-      </c>
-      <c r="J14" s="2" t="inlineStr">
-        <is>
-          <t>23</t>
-        </is>
-      </c>
-      <c r="K14" s="2" t="inlineStr">
-        <is>
-          <t>16750</t>
         </is>
       </c>
       <c r="L14" s="2" t="inlineStr">
@@ -5300,57 +5300,57 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
+          <t>23</t>
+        </is>
+      </c>
+      <c r="D15" s="2" t="inlineStr">
+        <is>
+          <t>16750</t>
+        </is>
+      </c>
+      <c r="E15" s="2" t="inlineStr">
+        <is>
+          <t>16750</t>
+        </is>
+      </c>
+      <c r="F15" s="2" t="inlineStr">
+        <is>
+          <t>16750</t>
+        </is>
+      </c>
+      <c r="G15" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H15" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I15" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J15" s="2" t="inlineStr">
+        <is>
           <t>36</t>
         </is>
       </c>
-      <c r="D15" s="2" t="inlineStr">
+      <c r="K15" s="2" t="inlineStr">
         <is>
           <t>24892</t>
         </is>
       </c>
-      <c r="E15" s="2" t="inlineStr">
+      <c r="L15" s="2" t="inlineStr">
         <is>
           <t>24892</t>
         </is>
       </c>
-      <c r="F15" s="2" t="inlineStr">
+      <c r="M15" s="2" t="inlineStr">
         <is>
           <t>24892</t>
-        </is>
-      </c>
-      <c r="G15" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H15" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I15" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J15" s="2" t="inlineStr">
-        <is>
-          <t>23</t>
-        </is>
-      </c>
-      <c r="K15" s="2" t="inlineStr">
-        <is>
-          <t>16750</t>
-        </is>
-      </c>
-      <c r="L15" s="2" t="inlineStr">
-        <is>
-          <t>16750</t>
-        </is>
-      </c>
-      <c r="M15" s="2" t="inlineStr">
-        <is>
-          <t>16750</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
@@ -5417,107 +5417,107 @@
       </c>
       <c r="C16" s="2" t="inlineStr">
         <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="D16" s="2" t="inlineStr">
+        <is>
+          <t>1305</t>
+        </is>
+      </c>
+      <c r="E16" s="2" t="inlineStr">
+        <is>
           <t>0</t>
         </is>
       </c>
-      <c r="D16" s="2" t="inlineStr">
+      <c r="F16" s="2" t="inlineStr">
+        <is>
+          <t>4012</t>
+        </is>
+      </c>
+      <c r="G16" s="2" t="inlineStr">
+        <is>
+          <t>9,6%</t>
+        </is>
+      </c>
+      <c r="H16" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="I16" s="2" t="inlineStr">
+        <is>
+          <t>29,53%</t>
+        </is>
+      </c>
+      <c r="J16" s="2" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="E16" s="2" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="F16" s="2" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="G16" s="2" t="inlineStr">
+      <c r="K16" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="L16" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="M16" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="N16" s="2" t="inlineStr">
         <is>
           <t>0,0%</t>
         </is>
       </c>
-      <c r="H16" s="2" t="inlineStr">
-        <is>
-          <t>—%</t>
-        </is>
-      </c>
-      <c r="I16" s="2" t="inlineStr">
-        <is>
-          <t>—%</t>
-        </is>
-      </c>
-      <c r="J16" s="2" t="inlineStr">
+      <c r="O16" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="P16" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="Q16" s="2" t="inlineStr">
         <is>
           <t>2</t>
         </is>
       </c>
-      <c r="K16" s="2" t="inlineStr">
+      <c r="R16" s="2" t="inlineStr">
         <is>
           <t>1305</t>
         </is>
       </c>
-      <c r="L16" s="2" t="inlineStr">
+      <c r="S16" s="2" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="M16" s="2" t="inlineStr">
-        <is>
-          <t>3945</t>
-        </is>
-      </c>
-      <c r="N16" s="2" t="inlineStr">
-        <is>
-          <t>9,6%</t>
-        </is>
-      </c>
-      <c r="O16" s="2" t="inlineStr">
+      <c r="T16" s="2" t="inlineStr">
+        <is>
+          <t>4009</t>
+        </is>
+      </c>
+      <c r="U16" s="2" t="inlineStr">
+        <is>
+          <t>3,91%</t>
+        </is>
+      </c>
+      <c r="V16" s="2" t="inlineStr">
         <is>
           <t>0,0%</t>
         </is>
       </c>
-      <c r="P16" s="2" t="inlineStr">
-        <is>
-          <t>29,03%</t>
-        </is>
-      </c>
-      <c r="Q16" s="2" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="R16" s="2" t="inlineStr">
-        <is>
-          <t>1305</t>
-        </is>
-      </c>
-      <c r="S16" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="T16" s="2" t="inlineStr">
-        <is>
-          <t>4031</t>
-        </is>
-      </c>
-      <c r="U16" s="2" t="inlineStr">
-        <is>
-          <t>3,91%</t>
-        </is>
-      </c>
-      <c r="V16" s="2" t="inlineStr">
-        <is>
-          <t>0,0%</t>
-        </is>
-      </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>12,07%</t>
+          <t>12,0%</t>
         </is>
       </c>
     </row>
@@ -5530,72 +5530,72 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
+          <t>17</t>
+        </is>
+      </c>
+      <c r="D17" s="2" t="inlineStr">
+        <is>
+          <t>12282</t>
+        </is>
+      </c>
+      <c r="E17" s="2" t="inlineStr">
+        <is>
+          <t>9575</t>
+        </is>
+      </c>
+      <c r="F17" s="2" t="inlineStr">
+        <is>
+          <t>13587</t>
+        </is>
+      </c>
+      <c r="G17" s="2" t="inlineStr">
+        <is>
+          <t>90,4%</t>
+        </is>
+      </c>
+      <c r="H17" s="2" t="inlineStr">
+        <is>
+          <t>70,47%</t>
+        </is>
+      </c>
+      <c r="I17" s="2" t="inlineStr">
+        <is>
+          <t>100,0%</t>
+        </is>
+      </c>
+      <c r="J17" s="2" t="inlineStr">
+        <is>
           <t>26</t>
         </is>
       </c>
-      <c r="D17" s="2" t="inlineStr">
+      <c r="K17" s="2" t="inlineStr">
         <is>
           <t>19813</t>
         </is>
       </c>
-      <c r="E17" s="2" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="F17" s="2" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="G17" s="2" t="inlineStr">
+      <c r="L17" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="M17" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="N17" s="2" t="inlineStr">
         <is>
           <t>100,0%</t>
         </is>
       </c>
-      <c r="H17" s="2" t="inlineStr">
-        <is>
-          <t>—%</t>
-        </is>
-      </c>
-      <c r="I17" s="2" t="inlineStr">
-        <is>
-          <t>—%</t>
-        </is>
-      </c>
-      <c r="J17" s="2" t="inlineStr">
-        <is>
-          <t>17</t>
-        </is>
-      </c>
-      <c r="K17" s="2" t="inlineStr">
-        <is>
-          <t>12282</t>
-        </is>
-      </c>
-      <c r="L17" s="2" t="inlineStr">
-        <is>
-          <t>9642</t>
-        </is>
-      </c>
-      <c r="M17" s="2" t="inlineStr">
-        <is>
-          <t>13587</t>
-        </is>
-      </c>
-      <c r="N17" s="2" t="inlineStr">
-        <is>
-          <t>90,4%</t>
-        </is>
-      </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>70,97%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>100,0%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -5610,7 +5610,7 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>29369</t>
+          <t>29391</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
@@ -5625,7 +5625,7 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>87,93%</t>
+          <t>88,0%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
@@ -5643,57 +5643,57 @@
       </c>
       <c r="C18" s="2" t="inlineStr">
         <is>
+          <t>19</t>
+        </is>
+      </c>
+      <c r="D18" s="2" t="inlineStr">
+        <is>
+          <t>13587</t>
+        </is>
+      </c>
+      <c r="E18" s="2" t="inlineStr">
+        <is>
+          <t>13587</t>
+        </is>
+      </c>
+      <c r="F18" s="2" t="inlineStr">
+        <is>
+          <t>13587</t>
+        </is>
+      </c>
+      <c r="G18" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H18" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I18" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J18" s="2" t="inlineStr">
+        <is>
           <t>26</t>
         </is>
       </c>
-      <c r="D18" s="2" t="inlineStr">
+      <c r="K18" s="2" t="inlineStr">
         <is>
           <t>19813</t>
         </is>
       </c>
-      <c r="E18" s="2" t="inlineStr">
+      <c r="L18" s="2" t="inlineStr">
         <is>
           <t>19813</t>
         </is>
       </c>
-      <c r="F18" s="2" t="inlineStr">
+      <c r="M18" s="2" t="inlineStr">
         <is>
           <t>19813</t>
-        </is>
-      </c>
-      <c r="G18" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H18" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I18" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J18" s="2" t="inlineStr">
-        <is>
-          <t>19</t>
-        </is>
-      </c>
-      <c r="K18" s="2" t="inlineStr">
-        <is>
-          <t>13587</t>
-        </is>
-      </c>
-      <c r="L18" s="2" t="inlineStr">
-        <is>
-          <t>13587</t>
-        </is>
-      </c>
-      <c r="M18" s="2" t="inlineStr">
-        <is>
-          <t>13587</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
@@ -5873,47 +5873,47 @@
       </c>
       <c r="C20" s="2" t="inlineStr">
         <is>
+          <t>27</t>
+        </is>
+      </c>
+      <c r="D20" s="2" t="inlineStr">
+        <is>
+          <t>19510</t>
+        </is>
+      </c>
+      <c r="E20" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="F20" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G20" s="2" t="inlineStr">
+        <is>
+          <t>100,0%</t>
+        </is>
+      </c>
+      <c r="H20" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="I20" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="J20" s="2" t="inlineStr">
+        <is>
           <t>19</t>
         </is>
       </c>
-      <c r="D20" s="2" t="inlineStr">
+      <c r="K20" s="2" t="inlineStr">
         <is>
           <t>13142</t>
-        </is>
-      </c>
-      <c r="E20" s="2" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="F20" s="2" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="G20" s="2" t="inlineStr">
-        <is>
-          <t>100,0%</t>
-        </is>
-      </c>
-      <c r="H20" s="2" t="inlineStr">
-        <is>
-          <t>—%</t>
-        </is>
-      </c>
-      <c r="I20" s="2" t="inlineStr">
-        <is>
-          <t>—%</t>
-        </is>
-      </c>
-      <c r="J20" s="2" t="inlineStr">
-        <is>
-          <t>27</t>
-        </is>
-      </c>
-      <c r="K20" s="2" t="inlineStr">
-        <is>
-          <t>19510</t>
         </is>
       </c>
       <c r="L20" s="2" t="inlineStr">
@@ -5986,57 +5986,57 @@
       </c>
       <c r="C21" s="2" t="inlineStr">
         <is>
+          <t>27</t>
+        </is>
+      </c>
+      <c r="D21" s="2" t="inlineStr">
+        <is>
+          <t>19510</t>
+        </is>
+      </c>
+      <c r="E21" s="2" t="inlineStr">
+        <is>
+          <t>19510</t>
+        </is>
+      </c>
+      <c r="F21" s="2" t="inlineStr">
+        <is>
+          <t>19510</t>
+        </is>
+      </c>
+      <c r="G21" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H21" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I21" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J21" s="2" t="inlineStr">
+        <is>
           <t>19</t>
         </is>
       </c>
-      <c r="D21" s="2" t="inlineStr">
+      <c r="K21" s="2" t="inlineStr">
         <is>
           <t>13142</t>
         </is>
       </c>
-      <c r="E21" s="2" t="inlineStr">
+      <c r="L21" s="2" t="inlineStr">
         <is>
           <t>13142</t>
         </is>
       </c>
-      <c r="F21" s="2" t="inlineStr">
+      <c r="M21" s="2" t="inlineStr">
         <is>
           <t>13142</t>
-        </is>
-      </c>
-      <c r="G21" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H21" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I21" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J21" s="2" t="inlineStr">
-        <is>
-          <t>27</t>
-        </is>
-      </c>
-      <c r="K21" s="2" t="inlineStr">
-        <is>
-          <t>19510</t>
-        </is>
-      </c>
-      <c r="L21" s="2" t="inlineStr">
-        <is>
-          <t>19510</t>
-        </is>
-      </c>
-      <c r="M21" s="2" t="inlineStr">
-        <is>
-          <t>19510</t>
         </is>
       </c>
       <c r="N21" s="2" t="inlineStr">
@@ -6108,102 +6108,102 @@
       </c>
       <c r="D22" s="2" t="inlineStr">
         <is>
+          <t>645</t>
+        </is>
+      </c>
+      <c r="E22" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="F22" s="2" t="inlineStr">
+        <is>
+          <t>3236</t>
+        </is>
+      </c>
+      <c r="G22" s="2" t="inlineStr">
+        <is>
+          <t>2,21%</t>
+        </is>
+      </c>
+      <c r="H22" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="I22" s="2" t="inlineStr">
+        <is>
+          <t>11,09%</t>
+        </is>
+      </c>
+      <c r="J22" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="K22" s="2" t="inlineStr">
+        <is>
           <t>944</t>
         </is>
       </c>
-      <c r="E22" s="2" t="inlineStr">
+      <c r="L22" s="2" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="F22" s="2" t="inlineStr">
-        <is>
-          <t>4595</t>
-        </is>
-      </c>
-      <c r="G22" s="2" t="inlineStr">
+      <c r="M22" s="2" t="inlineStr">
+        <is>
+          <t>5423</t>
+        </is>
+      </c>
+      <c r="N22" s="2" t="inlineStr">
         <is>
           <t>2,82%</t>
         </is>
       </c>
-      <c r="H22" s="2" t="inlineStr">
+      <c r="O22" s="2" t="inlineStr">
         <is>
           <t>0,0%</t>
         </is>
       </c>
-      <c r="I22" s="2" t="inlineStr">
-        <is>
-          <t>13,71%</t>
-        </is>
-      </c>
-      <c r="J22" s="2" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="K22" s="2" t="inlineStr">
-        <is>
-          <t>645</t>
-        </is>
-      </c>
-      <c r="L22" s="2" t="inlineStr">
+      <c r="P22" s="2" t="inlineStr">
+        <is>
+          <t>16,18%</t>
+        </is>
+      </c>
+      <c r="Q22" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="R22" s="2" t="inlineStr">
+        <is>
+          <t>1589</t>
+        </is>
+      </c>
+      <c r="S22" s="2" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="M22" s="2" t="inlineStr">
-        <is>
-          <t>3229</t>
-        </is>
-      </c>
-      <c r="N22" s="2" t="inlineStr">
-        <is>
-          <t>2,21%</t>
-        </is>
-      </c>
-      <c r="O22" s="2" t="inlineStr">
+      <c r="T22" s="2" t="inlineStr">
+        <is>
+          <t>5147</t>
+        </is>
+      </c>
+      <c r="U22" s="2" t="inlineStr">
+        <is>
+          <t>2,53%</t>
+        </is>
+      </c>
+      <c r="V22" s="2" t="inlineStr">
         <is>
           <t>0,0%</t>
         </is>
       </c>
-      <c r="P22" s="2" t="inlineStr">
-        <is>
-          <t>11,06%</t>
-        </is>
-      </c>
-      <c r="Q22" s="2" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="R22" s="2" t="inlineStr">
-        <is>
-          <t>1589</t>
-        </is>
-      </c>
-      <c r="S22" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="T22" s="2" t="inlineStr">
-        <is>
-          <t>5459</t>
-        </is>
-      </c>
-      <c r="U22" s="2" t="inlineStr">
-        <is>
-          <t>2,53%</t>
-        </is>
-      </c>
-      <c r="V22" s="2" t="inlineStr">
-        <is>
-          <t>0,0%</t>
-        </is>
-      </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>8,71%</t>
+          <t>8,21%</t>
         </is>
       </c>
     </row>
@@ -6216,74 +6216,74 @@
       </c>
       <c r="C23" s="2" t="inlineStr">
         <is>
+          <t>40</t>
+        </is>
+      </c>
+      <c r="D23" s="2" t="inlineStr">
+        <is>
+          <t>28546</t>
+        </is>
+      </c>
+      <c r="E23" s="2" t="inlineStr">
+        <is>
+          <t>25955</t>
+        </is>
+      </c>
+      <c r="F23" s="2" t="inlineStr">
+        <is>
+          <t>29191</t>
+        </is>
+      </c>
+      <c r="G23" s="2" t="inlineStr">
+        <is>
+          <t>97,79%</t>
+        </is>
+      </c>
+      <c r="H23" s="2" t="inlineStr">
+        <is>
+          <t>88,91%</t>
+        </is>
+      </c>
+      <c r="I23" s="2" t="inlineStr">
+        <is>
+          <t>100,0%</t>
+        </is>
+      </c>
+      <c r="J23" s="2" t="inlineStr">
+        <is>
           <t>46</t>
         </is>
       </c>
-      <c r="D23" s="2" t="inlineStr">
+      <c r="K23" s="2" t="inlineStr">
         <is>
           <t>32567</t>
         </is>
       </c>
-      <c r="E23" s="2" t="inlineStr">
-        <is>
-          <t>28916</t>
-        </is>
-      </c>
-      <c r="F23" s="2" t="inlineStr">
+      <c r="L23" s="2" t="inlineStr">
+        <is>
+          <t>28088</t>
+        </is>
+      </c>
+      <c r="M23" s="2" t="inlineStr">
         <is>
           <t>33511</t>
         </is>
       </c>
-      <c r="G23" s="2" t="inlineStr">
+      <c r="N23" s="2" t="inlineStr">
         <is>
           <t>97,18%</t>
         </is>
       </c>
-      <c r="H23" s="2" t="inlineStr">
-        <is>
-          <t>86,29%</t>
-        </is>
-      </c>
-      <c r="I23" s="2" t="inlineStr">
+      <c r="O23" s="2" t="inlineStr">
+        <is>
+          <t>83,82%</t>
+        </is>
+      </c>
+      <c r="P23" s="2" t="inlineStr">
         <is>
           <t>100,0%</t>
         </is>
       </c>
-      <c r="J23" s="2" t="inlineStr">
-        <is>
-          <t>40</t>
-        </is>
-      </c>
-      <c r="K23" s="2" t="inlineStr">
-        <is>
-          <t>28546</t>
-        </is>
-      </c>
-      <c r="L23" s="2" t="inlineStr">
-        <is>
-          <t>25962</t>
-        </is>
-      </c>
-      <c r="M23" s="2" t="inlineStr">
-        <is>
-          <t>29191</t>
-        </is>
-      </c>
-      <c r="N23" s="2" t="inlineStr">
-        <is>
-          <t>97,79%</t>
-        </is>
-      </c>
-      <c r="O23" s="2" t="inlineStr">
-        <is>
-          <t>88,94%</t>
-        </is>
-      </c>
-      <c r="P23" s="2" t="inlineStr">
-        <is>
-          <t>100,0%</t>
-        </is>
-      </c>
       <c r="Q23" s="2" t="inlineStr">
         <is>
           <t>86</t>
@@ -6296,7 +6296,7 @@
       </c>
       <c r="S23" s="2" t="inlineStr">
         <is>
-          <t>57243</t>
+          <t>57555</t>
         </is>
       </c>
       <c r="T23" s="2" t="inlineStr">
@@ -6311,7 +6311,7 @@
       </c>
       <c r="V23" s="2" t="inlineStr">
         <is>
-          <t>91,29%</t>
+          <t>91,79%</t>
         </is>
       </c>
       <c r="W23" s="2" t="inlineStr">
@@ -6329,57 +6329,57 @@
       </c>
       <c r="C24" s="2" t="inlineStr">
         <is>
+          <t>41</t>
+        </is>
+      </c>
+      <c r="D24" s="2" t="inlineStr">
+        <is>
+          <t>29191</t>
+        </is>
+      </c>
+      <c r="E24" s="2" t="inlineStr">
+        <is>
+          <t>29191</t>
+        </is>
+      </c>
+      <c r="F24" s="2" t="inlineStr">
+        <is>
+          <t>29191</t>
+        </is>
+      </c>
+      <c r="G24" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H24" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I24" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J24" s="2" t="inlineStr">
+        <is>
           <t>47</t>
         </is>
       </c>
-      <c r="D24" s="2" t="inlineStr">
+      <c r="K24" s="2" t="inlineStr">
         <is>
           <t>33511</t>
         </is>
       </c>
-      <c r="E24" s="2" t="inlineStr">
+      <c r="L24" s="2" t="inlineStr">
         <is>
           <t>33511</t>
         </is>
       </c>
-      <c r="F24" s="2" t="inlineStr">
+      <c r="M24" s="2" t="inlineStr">
         <is>
           <t>33511</t>
-        </is>
-      </c>
-      <c r="G24" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H24" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I24" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J24" s="2" t="inlineStr">
-        <is>
-          <t>41</t>
-        </is>
-      </c>
-      <c r="K24" s="2" t="inlineStr">
-        <is>
-          <t>29191</t>
-        </is>
-      </c>
-      <c r="L24" s="2" t="inlineStr">
-        <is>
-          <t>29191</t>
-        </is>
-      </c>
-      <c r="M24" s="2" t="inlineStr">
-        <is>
-          <t>29191</t>
         </is>
       </c>
       <c r="N24" s="2" t="inlineStr">
@@ -6451,102 +6451,102 @@
       </c>
       <c r="D25" s="2" t="inlineStr">
         <is>
+          <t>652</t>
+        </is>
+      </c>
+      <c r="E25" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="F25" s="2" t="inlineStr">
+        <is>
+          <t>3301</t>
+        </is>
+      </c>
+      <c r="G25" s="2" t="inlineStr">
+        <is>
+          <t>2,43%</t>
+        </is>
+      </c>
+      <c r="H25" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="I25" s="2" t="inlineStr">
+        <is>
+          <t>12,27%</t>
+        </is>
+      </c>
+      <c r="J25" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="K25" s="2" t="inlineStr">
+        <is>
           <t>582</t>
         </is>
       </c>
-      <c r="E25" s="2" t="inlineStr">
+      <c r="L25" s="2" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="F25" s="2" t="inlineStr">
-        <is>
-          <t>3228</t>
-        </is>
-      </c>
-      <c r="G25" s="2" t="inlineStr">
+      <c r="M25" s="2" t="inlineStr">
+        <is>
+          <t>2606</t>
+        </is>
+      </c>
+      <c r="N25" s="2" t="inlineStr">
         <is>
           <t>2,39%</t>
         </is>
       </c>
-      <c r="H25" s="2" t="inlineStr">
+      <c r="O25" s="2" t="inlineStr">
         <is>
           <t>0,0%</t>
         </is>
       </c>
-      <c r="I25" s="2" t="inlineStr">
-        <is>
-          <t>13,26%</t>
-        </is>
-      </c>
-      <c r="J25" s="2" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="K25" s="2" t="inlineStr">
-        <is>
-          <t>652</t>
-        </is>
-      </c>
-      <c r="L25" s="2" t="inlineStr">
+      <c r="P25" s="2" t="inlineStr">
+        <is>
+          <t>10,7%</t>
+        </is>
+      </c>
+      <c r="Q25" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="R25" s="2" t="inlineStr">
+        <is>
+          <t>1234</t>
+        </is>
+      </c>
+      <c r="S25" s="2" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="M25" s="2" t="inlineStr">
-        <is>
-          <t>3262</t>
-        </is>
-      </c>
-      <c r="N25" s="2" t="inlineStr">
-        <is>
-          <t>2,43%</t>
-        </is>
-      </c>
-      <c r="O25" s="2" t="inlineStr">
+      <c r="T25" s="2" t="inlineStr">
+        <is>
+          <t>3857</t>
+        </is>
+      </c>
+      <c r="U25" s="2" t="inlineStr">
+        <is>
+          <t>2,41%</t>
+        </is>
+      </c>
+      <c r="V25" s="2" t="inlineStr">
         <is>
           <t>0,0%</t>
         </is>
       </c>
-      <c r="P25" s="2" t="inlineStr">
-        <is>
-          <t>12,12%</t>
-        </is>
-      </c>
-      <c r="Q25" s="2" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="R25" s="2" t="inlineStr">
-        <is>
-          <t>1234</t>
-        </is>
-      </c>
-      <c r="S25" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="T25" s="2" t="inlineStr">
-        <is>
-          <t>4633</t>
-        </is>
-      </c>
-      <c r="U25" s="2" t="inlineStr">
-        <is>
-          <t>2,41%</t>
-        </is>
-      </c>
-      <c r="V25" s="2" t="inlineStr">
-        <is>
-          <t>0,0%</t>
-        </is>
-      </c>
       <c r="W25" s="2" t="inlineStr">
         <is>
-          <t>9,04%</t>
+          <t>7,53%</t>
         </is>
       </c>
     </row>
@@ -6559,74 +6559,74 @@
       </c>
       <c r="C26" s="2" t="inlineStr">
         <is>
+          <t>38</t>
+        </is>
+      </c>
+      <c r="D26" s="2" t="inlineStr">
+        <is>
+          <t>26252</t>
+        </is>
+      </c>
+      <c r="E26" s="2" t="inlineStr">
+        <is>
+          <t>23603</t>
+        </is>
+      </c>
+      <c r="F26" s="2" t="inlineStr">
+        <is>
+          <t>26904</t>
+        </is>
+      </c>
+      <c r="G26" s="2" t="inlineStr">
+        <is>
+          <t>97,57%</t>
+        </is>
+      </c>
+      <c r="H26" s="2" t="inlineStr">
+        <is>
+          <t>87,73%</t>
+        </is>
+      </c>
+      <c r="I26" s="2" t="inlineStr">
+        <is>
+          <t>100,0%</t>
+        </is>
+      </c>
+      <c r="J26" s="2" t="inlineStr">
+        <is>
           <t>36</t>
         </is>
       </c>
-      <c r="D26" s="2" t="inlineStr">
+      <c r="K26" s="2" t="inlineStr">
         <is>
           <t>23768</t>
         </is>
       </c>
-      <c r="E26" s="2" t="inlineStr">
-        <is>
-          <t>21122</t>
-        </is>
-      </c>
-      <c r="F26" s="2" t="inlineStr">
+      <c r="L26" s="2" t="inlineStr">
+        <is>
+          <t>21744</t>
+        </is>
+      </c>
+      <c r="M26" s="2" t="inlineStr">
         <is>
           <t>24350</t>
         </is>
       </c>
-      <c r="G26" s="2" t="inlineStr">
+      <c r="N26" s="2" t="inlineStr">
         <is>
           <t>97,61%</t>
         </is>
       </c>
-      <c r="H26" s="2" t="inlineStr">
-        <is>
-          <t>86,74%</t>
-        </is>
-      </c>
-      <c r="I26" s="2" t="inlineStr">
+      <c r="O26" s="2" t="inlineStr">
+        <is>
+          <t>89,3%</t>
+        </is>
+      </c>
+      <c r="P26" s="2" t="inlineStr">
         <is>
           <t>100,0%</t>
         </is>
       </c>
-      <c r="J26" s="2" t="inlineStr">
-        <is>
-          <t>38</t>
-        </is>
-      </c>
-      <c r="K26" s="2" t="inlineStr">
-        <is>
-          <t>26252</t>
-        </is>
-      </c>
-      <c r="L26" s="2" t="inlineStr">
-        <is>
-          <t>23642</t>
-        </is>
-      </c>
-      <c r="M26" s="2" t="inlineStr">
-        <is>
-          <t>26904</t>
-        </is>
-      </c>
-      <c r="N26" s="2" t="inlineStr">
-        <is>
-          <t>97,57%</t>
-        </is>
-      </c>
-      <c r="O26" s="2" t="inlineStr">
-        <is>
-          <t>87,88%</t>
-        </is>
-      </c>
-      <c r="P26" s="2" t="inlineStr">
-        <is>
-          <t>100,0%</t>
-        </is>
-      </c>
       <c r="Q26" s="2" t="inlineStr">
         <is>
           <t>74</t>
@@ -6639,7 +6639,7 @@
       </c>
       <c r="S26" s="2" t="inlineStr">
         <is>
-          <t>46622</t>
+          <t>47398</t>
         </is>
       </c>
       <c r="T26" s="2" t="inlineStr">
@@ -6654,7 +6654,7 @@
       </c>
       <c r="V26" s="2" t="inlineStr">
         <is>
-          <t>90,96%</t>
+          <t>92,47%</t>
         </is>
       </c>
       <c r="W26" s="2" t="inlineStr">
@@ -6672,57 +6672,57 @@
       </c>
       <c r="C27" s="2" t="inlineStr">
         <is>
+          <t>39</t>
+        </is>
+      </c>
+      <c r="D27" s="2" t="inlineStr">
+        <is>
+          <t>26904</t>
+        </is>
+      </c>
+      <c r="E27" s="2" t="inlineStr">
+        <is>
+          <t>26904</t>
+        </is>
+      </c>
+      <c r="F27" s="2" t="inlineStr">
+        <is>
+          <t>26904</t>
+        </is>
+      </c>
+      <c r="G27" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H27" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I27" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J27" s="2" t="inlineStr">
+        <is>
           <t>37</t>
         </is>
       </c>
-      <c r="D27" s="2" t="inlineStr">
+      <c r="K27" s="2" t="inlineStr">
         <is>
           <t>24350</t>
         </is>
       </c>
-      <c r="E27" s="2" t="inlineStr">
+      <c r="L27" s="2" t="inlineStr">
         <is>
           <t>24350</t>
         </is>
       </c>
-      <c r="F27" s="2" t="inlineStr">
+      <c r="M27" s="2" t="inlineStr">
         <is>
           <t>24350</t>
-        </is>
-      </c>
-      <c r="G27" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H27" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I27" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J27" s="2" t="inlineStr">
-        <is>
-          <t>39</t>
-        </is>
-      </c>
-      <c r="K27" s="2" t="inlineStr">
-        <is>
-          <t>26904</t>
-        </is>
-      </c>
-      <c r="L27" s="2" t="inlineStr">
-        <is>
-          <t>26904</t>
-        </is>
-      </c>
-      <c r="M27" s="2" t="inlineStr">
-        <is>
-          <t>26904</t>
         </is>
       </c>
       <c r="N27" s="2" t="inlineStr">
@@ -6789,72 +6789,72 @@
       </c>
       <c r="C28" s="2" t="inlineStr">
         <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="D28" s="2" t="inlineStr">
+        <is>
+          <t>4097</t>
+        </is>
+      </c>
+      <c r="E28" s="2" t="inlineStr">
+        <is>
+          <t>1547</t>
+        </is>
+      </c>
+      <c r="F28" s="2" t="inlineStr">
+        <is>
+          <t>8784</t>
+        </is>
+      </c>
+      <c r="G28" s="2" t="inlineStr">
+        <is>
+          <t>2,15%</t>
+        </is>
+      </c>
+      <c r="H28" s="2" t="inlineStr">
+        <is>
+          <t>0,81%</t>
+        </is>
+      </c>
+      <c r="I28" s="2" t="inlineStr">
+        <is>
+          <t>4,6%</t>
+        </is>
+      </c>
+      <c r="J28" s="2" t="inlineStr">
+        <is>
           <t>5</t>
         </is>
       </c>
-      <c r="D28" s="2" t="inlineStr">
+      <c r="K28" s="2" t="inlineStr">
         <is>
           <t>3296</t>
         </is>
       </c>
-      <c r="E28" s="2" t="inlineStr">
-        <is>
-          <t>1193</t>
-        </is>
-      </c>
-      <c r="F28" s="2" t="inlineStr">
-        <is>
-          <t>7245</t>
-        </is>
-      </c>
-      <c r="G28" s="2" t="inlineStr">
+      <c r="L28" s="2" t="inlineStr">
+        <is>
+          <t>1211</t>
+        </is>
+      </c>
+      <c r="M28" s="2" t="inlineStr">
+        <is>
+          <t>7613</t>
+        </is>
+      </c>
+      <c r="N28" s="2" t="inlineStr">
         <is>
           <t>1,76%</t>
         </is>
       </c>
-      <c r="H28" s="2" t="inlineStr">
-        <is>
-          <t>0,64%</t>
-        </is>
-      </c>
-      <c r="I28" s="2" t="inlineStr">
-        <is>
-          <t>3,87%</t>
-        </is>
-      </c>
-      <c r="J28" s="2" t="inlineStr">
-        <is>
-          <t>6</t>
-        </is>
-      </c>
-      <c r="K28" s="2" t="inlineStr">
-        <is>
-          <t>4097</t>
-        </is>
-      </c>
-      <c r="L28" s="2" t="inlineStr">
-        <is>
-          <t>1314</t>
-        </is>
-      </c>
-      <c r="M28" s="2" t="inlineStr">
-        <is>
-          <t>8057</t>
-        </is>
-      </c>
-      <c r="N28" s="2" t="inlineStr">
-        <is>
-          <t>2,15%</t>
-        </is>
-      </c>
       <c r="O28" s="2" t="inlineStr">
         <is>
-          <t>0,69%</t>
+          <t>0,65%</t>
         </is>
       </c>
       <c r="P28" s="2" t="inlineStr">
         <is>
-          <t>4,22%</t>
+          <t>4,07%</t>
         </is>
       </c>
       <c r="Q28" s="2" t="inlineStr">
@@ -6869,12 +6869,12 @@
       </c>
       <c r="S28" s="2" t="inlineStr">
         <is>
-          <t>3803</t>
+          <t>3915</t>
         </is>
       </c>
       <c r="T28" s="2" t="inlineStr">
         <is>
-          <t>13004</t>
+          <t>12980</t>
         </is>
       </c>
       <c r="U28" s="2" t="inlineStr">
@@ -6884,7 +6884,7 @@
       </c>
       <c r="V28" s="2" t="inlineStr">
         <is>
-          <t>1,01%</t>
+          <t>1,04%</t>
         </is>
       </c>
       <c r="W28" s="2" t="inlineStr">
@@ -6907,67 +6907,67 @@
       </c>
       <c r="D29" s="2" t="inlineStr">
         <is>
+          <t>186753</t>
+        </is>
+      </c>
+      <c r="E29" s="2" t="inlineStr">
+        <is>
+          <t>182066</t>
+        </is>
+      </c>
+      <c r="F29" s="2" t="inlineStr">
+        <is>
+          <t>189303</t>
+        </is>
+      </c>
+      <c r="G29" s="2" t="inlineStr">
+        <is>
+          <t>97,85%</t>
+        </is>
+      </c>
+      <c r="H29" s="2" t="inlineStr">
+        <is>
+          <t>95,4%</t>
+        </is>
+      </c>
+      <c r="I29" s="2" t="inlineStr">
+        <is>
+          <t>99,19%</t>
+        </is>
+      </c>
+      <c r="J29" s="2" t="inlineStr">
+        <is>
+          <t>264</t>
+        </is>
+      </c>
+      <c r="K29" s="2" t="inlineStr">
+        <is>
           <t>183696</t>
         </is>
       </c>
-      <c r="E29" s="2" t="inlineStr">
-        <is>
-          <t>179747</t>
-        </is>
-      </c>
-      <c r="F29" s="2" t="inlineStr">
-        <is>
-          <t>185799</t>
-        </is>
-      </c>
-      <c r="G29" s="2" t="inlineStr">
+      <c r="L29" s="2" t="inlineStr">
+        <is>
+          <t>179379</t>
+        </is>
+      </c>
+      <c r="M29" s="2" t="inlineStr">
+        <is>
+          <t>185781</t>
+        </is>
+      </c>
+      <c r="N29" s="2" t="inlineStr">
         <is>
           <t>98,24%</t>
         </is>
       </c>
-      <c r="H29" s="2" t="inlineStr">
-        <is>
-          <t>96,13%</t>
-        </is>
-      </c>
-      <c r="I29" s="2" t="inlineStr">
-        <is>
-          <t>99,36%</t>
-        </is>
-      </c>
-      <c r="J29" s="2" t="inlineStr">
-        <is>
-          <t>264</t>
-        </is>
-      </c>
-      <c r="K29" s="2" t="inlineStr">
-        <is>
-          <t>186753</t>
-        </is>
-      </c>
-      <c r="L29" s="2" t="inlineStr">
-        <is>
-          <t>182793</t>
-        </is>
-      </c>
-      <c r="M29" s="2" t="inlineStr">
-        <is>
-          <t>189536</t>
-        </is>
-      </c>
-      <c r="N29" s="2" t="inlineStr">
-        <is>
-          <t>97,85%</t>
-        </is>
-      </c>
       <c r="O29" s="2" t="inlineStr">
         <is>
-          <t>95,78%</t>
+          <t>95,93%</t>
         </is>
       </c>
       <c r="P29" s="2" t="inlineStr">
         <is>
-          <t>99,31%</t>
+          <t>99,35%</t>
         </is>
       </c>
       <c r="Q29" s="2" t="inlineStr">
@@ -6982,12 +6982,12 @@
       </c>
       <c r="S29" s="2" t="inlineStr">
         <is>
-          <t>364838</t>
+          <t>364862</t>
         </is>
       </c>
       <c r="T29" s="2" t="inlineStr">
         <is>
-          <t>374039</t>
+          <t>373927</t>
         </is>
       </c>
       <c r="U29" s="2" t="inlineStr">
@@ -7002,7 +7002,7 @@
       </c>
       <c r="W29" s="2" t="inlineStr">
         <is>
-          <t>98,99%</t>
+          <t>98,96%</t>
         </is>
       </c>
     </row>
@@ -7015,57 +7015,57 @@
       </c>
       <c r="C30" s="2" t="inlineStr">
         <is>
+          <t>270</t>
+        </is>
+      </c>
+      <c r="D30" s="2" t="inlineStr">
+        <is>
+          <t>190850</t>
+        </is>
+      </c>
+      <c r="E30" s="2" t="inlineStr">
+        <is>
+          <t>190850</t>
+        </is>
+      </c>
+      <c r="F30" s="2" t="inlineStr">
+        <is>
+          <t>190850</t>
+        </is>
+      </c>
+      <c r="G30" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H30" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I30" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J30" s="2" t="inlineStr">
+        <is>
           <t>269</t>
         </is>
       </c>
-      <c r="D30" s="2" t="inlineStr">
+      <c r="K30" s="2" t="inlineStr">
         <is>
           <t>186992</t>
         </is>
       </c>
-      <c r="E30" s="2" t="inlineStr">
+      <c r="L30" s="2" t="inlineStr">
         <is>
           <t>186992</t>
         </is>
       </c>
-      <c r="F30" s="2" t="inlineStr">
+      <c r="M30" s="2" t="inlineStr">
         <is>
           <t>186992</t>
-        </is>
-      </c>
-      <c r="G30" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H30" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I30" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J30" s="2" t="inlineStr">
-        <is>
-          <t>270</t>
-        </is>
-      </c>
-      <c r="K30" s="2" t="inlineStr">
-        <is>
-          <t>190850</t>
-        </is>
-      </c>
-      <c r="L30" s="2" t="inlineStr">
-        <is>
-          <t>190850</t>
-        </is>
-      </c>
-      <c r="M30" s="2" t="inlineStr">
-        <is>
-          <t>190850</t>
         </is>
       </c>
       <c r="N30" s="2" t="inlineStr">
@@ -7189,7 +7189,7 @@
       <c r="B1" s="2" t="n"/>
       <c r="C1" s="3" t="inlineStr">
         <is>
-          <t>Niña</t>
+          <t>Niño</t>
         </is>
       </c>
       <c r="D1" s="3" t="n"/>
@@ -7200,7 +7200,7 @@
       <c r="I1" s="3" t="n"/>
       <c r="J1" s="3" t="inlineStr">
         <is>
-          <t>Niño</t>
+          <t>Niña</t>
         </is>
       </c>
       <c r="K1" s="3" t="n"/>
@@ -7481,47 +7481,47 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
+          <t>35</t>
+        </is>
+      </c>
+      <c r="D5" s="2" t="inlineStr">
+        <is>
+          <t>24501</t>
+        </is>
+      </c>
+      <c r="E5" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="F5" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G5" s="2" t="inlineStr">
+        <is>
+          <t>100,0%</t>
+        </is>
+      </c>
+      <c r="H5" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="I5" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="J5" s="2" t="inlineStr">
+        <is>
           <t>30</t>
         </is>
       </c>
-      <c r="D5" s="2" t="inlineStr">
+      <c r="K5" s="2" t="inlineStr">
         <is>
           <t>19555</t>
-        </is>
-      </c>
-      <c r="E5" s="2" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="F5" s="2" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="G5" s="2" t="inlineStr">
-        <is>
-          <t>100,0%</t>
-        </is>
-      </c>
-      <c r="H5" s="2" t="inlineStr">
-        <is>
-          <t>—%</t>
-        </is>
-      </c>
-      <c r="I5" s="2" t="inlineStr">
-        <is>
-          <t>—%</t>
-        </is>
-      </c>
-      <c r="J5" s="2" t="inlineStr">
-        <is>
-          <t>35</t>
-        </is>
-      </c>
-      <c r="K5" s="2" t="inlineStr">
-        <is>
-          <t>24501</t>
         </is>
       </c>
       <c r="L5" s="2" t="inlineStr">
@@ -7594,57 +7594,57 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
+          <t>35</t>
+        </is>
+      </c>
+      <c r="D6" s="2" t="inlineStr">
+        <is>
+          <t>24501</t>
+        </is>
+      </c>
+      <c r="E6" s="2" t="inlineStr">
+        <is>
+          <t>24501</t>
+        </is>
+      </c>
+      <c r="F6" s="2" t="inlineStr">
+        <is>
+          <t>24501</t>
+        </is>
+      </c>
+      <c r="G6" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H6" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I6" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J6" s="2" t="inlineStr">
+        <is>
           <t>30</t>
         </is>
       </c>
-      <c r="D6" s="2" t="inlineStr">
+      <c r="K6" s="2" t="inlineStr">
         <is>
           <t>19555</t>
         </is>
       </c>
-      <c r="E6" s="2" t="inlineStr">
+      <c r="L6" s="2" t="inlineStr">
         <is>
           <t>19555</t>
         </is>
       </c>
-      <c r="F6" s="2" t="inlineStr">
+      <c r="M6" s="2" t="inlineStr">
         <is>
           <t>19555</t>
-        </is>
-      </c>
-      <c r="G6" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H6" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I6" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J6" s="2" t="inlineStr">
-        <is>
-          <t>35</t>
-        </is>
-      </c>
-      <c r="K6" s="2" t="inlineStr">
-        <is>
-          <t>24501</t>
-        </is>
-      </c>
-      <c r="L6" s="2" t="inlineStr">
-        <is>
-          <t>24501</t>
-        </is>
-      </c>
-      <c r="M6" s="2" t="inlineStr">
-        <is>
-          <t>24501</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
@@ -7711,107 +7711,107 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="D7" s="2" t="inlineStr">
+        <is>
+          <t>1399</t>
+        </is>
+      </c>
+      <c r="E7" s="2" t="inlineStr">
+        <is>
           <t>0</t>
         </is>
       </c>
-      <c r="D7" s="2" t="inlineStr">
+      <c r="F7" s="2" t="inlineStr">
+        <is>
+          <t>4989</t>
+        </is>
+      </c>
+      <c r="G7" s="2" t="inlineStr">
+        <is>
+          <t>6,0%</t>
+        </is>
+      </c>
+      <c r="H7" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="I7" s="2" t="inlineStr">
+        <is>
+          <t>21,39%</t>
+        </is>
+      </c>
+      <c r="J7" s="2" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="E7" s="2" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="F7" s="2" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="G7" s="2" t="inlineStr">
+      <c r="K7" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="L7" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="M7" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="N7" s="2" t="inlineStr">
         <is>
           <t>0,0%</t>
         </is>
       </c>
-      <c r="H7" s="2" t="inlineStr">
-        <is>
-          <t>—%</t>
-        </is>
-      </c>
-      <c r="I7" s="2" t="inlineStr">
-        <is>
-          <t>—%</t>
-        </is>
-      </c>
-      <c r="J7" s="2" t="inlineStr">
+      <c r="O7" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="P7" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="Q7" s="2" t="inlineStr">
         <is>
           <t>2</t>
         </is>
       </c>
-      <c r="K7" s="2" t="inlineStr">
+      <c r="R7" s="2" t="inlineStr">
         <is>
           <t>1399</t>
         </is>
       </c>
-      <c r="L7" s="2" t="inlineStr">
+      <c r="S7" s="2" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="M7" s="2" t="inlineStr">
-        <is>
-          <t>4298</t>
-        </is>
-      </c>
-      <c r="N7" s="2" t="inlineStr">
-        <is>
-          <t>6,0%</t>
-        </is>
-      </c>
-      <c r="O7" s="2" t="inlineStr">
+      <c r="T7" s="2" t="inlineStr">
+        <is>
+          <t>4398</t>
+        </is>
+      </c>
+      <c r="U7" s="2" t="inlineStr">
+        <is>
+          <t>2,6%</t>
+        </is>
+      </c>
+      <c r="V7" s="2" t="inlineStr">
         <is>
           <t>0,0%</t>
         </is>
       </c>
-      <c r="P7" s="2" t="inlineStr">
-        <is>
-          <t>18,43%</t>
-        </is>
-      </c>
-      <c r="Q7" s="2" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="R7" s="2" t="inlineStr">
-        <is>
-          <t>1399</t>
-        </is>
-      </c>
-      <c r="S7" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="T7" s="2" t="inlineStr">
-        <is>
-          <t>4868</t>
-        </is>
-      </c>
-      <c r="U7" s="2" t="inlineStr">
-        <is>
-          <t>2,6%</t>
-        </is>
-      </c>
-      <c r="V7" s="2" t="inlineStr">
-        <is>
-          <t>0,0%</t>
-        </is>
-      </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>9,06%</t>
+          <t>8,19%</t>
         </is>
       </c>
     </row>
@@ -7824,72 +7824,72 @@
       </c>
       <c r="C8" s="2" t="inlineStr">
         <is>
+          <t>33</t>
+        </is>
+      </c>
+      <c r="D8" s="2" t="inlineStr">
+        <is>
+          <t>21919</t>
+        </is>
+      </c>
+      <c r="E8" s="2" t="inlineStr">
+        <is>
+          <t>18329</t>
+        </is>
+      </c>
+      <c r="F8" s="2" t="inlineStr">
+        <is>
+          <t>23318</t>
+        </is>
+      </c>
+      <c r="G8" s="2" t="inlineStr">
+        <is>
+          <t>94,0%</t>
+        </is>
+      </c>
+      <c r="H8" s="2" t="inlineStr">
+        <is>
+          <t>78,61%</t>
+        </is>
+      </c>
+      <c r="I8" s="2" t="inlineStr">
+        <is>
+          <t>100,0%</t>
+        </is>
+      </c>
+      <c r="J8" s="2" t="inlineStr">
+        <is>
           <t>46</t>
         </is>
       </c>
-      <c r="D8" s="2" t="inlineStr">
+      <c r="K8" s="2" t="inlineStr">
         <is>
           <t>30413</t>
         </is>
       </c>
-      <c r="E8" s="2" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="F8" s="2" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="G8" s="2" t="inlineStr">
+      <c r="L8" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="M8" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="N8" s="2" t="inlineStr">
         <is>
           <t>100,0%</t>
         </is>
       </c>
-      <c r="H8" s="2" t="inlineStr">
-        <is>
-          <t>—%</t>
-        </is>
-      </c>
-      <c r="I8" s="2" t="inlineStr">
-        <is>
-          <t>—%</t>
-        </is>
-      </c>
-      <c r="J8" s="2" t="inlineStr">
-        <is>
-          <t>33</t>
-        </is>
-      </c>
-      <c r="K8" s="2" t="inlineStr">
-        <is>
-          <t>21919</t>
-        </is>
-      </c>
-      <c r="L8" s="2" t="inlineStr">
-        <is>
-          <t>19020</t>
-        </is>
-      </c>
-      <c r="M8" s="2" t="inlineStr">
-        <is>
-          <t>23318</t>
-        </is>
-      </c>
-      <c r="N8" s="2" t="inlineStr">
-        <is>
-          <t>94,0%</t>
-        </is>
-      </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>81,57%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>100,0%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -7904,7 +7904,7 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>48863</t>
+          <t>49333</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
@@ -7919,7 +7919,7 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>90,94%</t>
+          <t>91,81%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
@@ -7937,57 +7937,57 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
+          <t>35</t>
+        </is>
+      </c>
+      <c r="D9" s="2" t="inlineStr">
+        <is>
+          <t>23318</t>
+        </is>
+      </c>
+      <c r="E9" s="2" t="inlineStr">
+        <is>
+          <t>23318</t>
+        </is>
+      </c>
+      <c r="F9" s="2" t="inlineStr">
+        <is>
+          <t>23318</t>
+        </is>
+      </c>
+      <c r="G9" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H9" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I9" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J9" s="2" t="inlineStr">
+        <is>
           <t>46</t>
         </is>
       </c>
-      <c r="D9" s="2" t="inlineStr">
+      <c r="K9" s="2" t="inlineStr">
         <is>
           <t>30413</t>
         </is>
       </c>
-      <c r="E9" s="2" t="inlineStr">
+      <c r="L9" s="2" t="inlineStr">
         <is>
           <t>30413</t>
         </is>
       </c>
-      <c r="F9" s="2" t="inlineStr">
+      <c r="M9" s="2" t="inlineStr">
         <is>
           <t>30413</t>
-        </is>
-      </c>
-      <c r="G9" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H9" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I9" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J9" s="2" t="inlineStr">
-        <is>
-          <t>35</t>
-        </is>
-      </c>
-      <c r="K9" s="2" t="inlineStr">
-        <is>
-          <t>23318</t>
-        </is>
-      </c>
-      <c r="L9" s="2" t="inlineStr">
-        <is>
-          <t>23318</t>
-        </is>
-      </c>
-      <c r="M9" s="2" t="inlineStr">
-        <is>
-          <t>23318</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
@@ -8167,47 +8167,47 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
+          <t>14</t>
+        </is>
+      </c>
+      <c r="D11" s="2" t="inlineStr">
+        <is>
+          <t>9727</t>
+        </is>
+      </c>
+      <c r="E11" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="F11" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G11" s="2" t="inlineStr">
+        <is>
+          <t>100,0%</t>
+        </is>
+      </c>
+      <c r="H11" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="I11" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="J11" s="2" t="inlineStr">
+        <is>
           <t>15</t>
         </is>
       </c>
-      <c r="D11" s="2" t="inlineStr">
+      <c r="K11" s="2" t="inlineStr">
         <is>
           <t>10287</t>
-        </is>
-      </c>
-      <c r="E11" s="2" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="F11" s="2" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="G11" s="2" t="inlineStr">
-        <is>
-          <t>100,0%</t>
-        </is>
-      </c>
-      <c r="H11" s="2" t="inlineStr">
-        <is>
-          <t>—%</t>
-        </is>
-      </c>
-      <c r="I11" s="2" t="inlineStr">
-        <is>
-          <t>—%</t>
-        </is>
-      </c>
-      <c r="J11" s="2" t="inlineStr">
-        <is>
-          <t>14</t>
-        </is>
-      </c>
-      <c r="K11" s="2" t="inlineStr">
-        <is>
-          <t>9727</t>
         </is>
       </c>
       <c r="L11" s="2" t="inlineStr">
@@ -8280,57 +8280,57 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
+          <t>14</t>
+        </is>
+      </c>
+      <c r="D12" s="2" t="inlineStr">
+        <is>
+          <t>9727</t>
+        </is>
+      </c>
+      <c r="E12" s="2" t="inlineStr">
+        <is>
+          <t>9727</t>
+        </is>
+      </c>
+      <c r="F12" s="2" t="inlineStr">
+        <is>
+          <t>9727</t>
+        </is>
+      </c>
+      <c r="G12" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H12" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I12" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J12" s="2" t="inlineStr">
+        <is>
           <t>15</t>
         </is>
       </c>
-      <c r="D12" s="2" t="inlineStr">
+      <c r="K12" s="2" t="inlineStr">
         <is>
           <t>10287</t>
         </is>
       </c>
-      <c r="E12" s="2" t="inlineStr">
+      <c r="L12" s="2" t="inlineStr">
         <is>
           <t>10287</t>
         </is>
       </c>
-      <c r="F12" s="2" t="inlineStr">
+      <c r="M12" s="2" t="inlineStr">
         <is>
           <t>10287</t>
-        </is>
-      </c>
-      <c r="G12" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H12" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I12" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J12" s="2" t="inlineStr">
-        <is>
-          <t>14</t>
-        </is>
-      </c>
-      <c r="K12" s="2" t="inlineStr">
-        <is>
-          <t>9727</t>
-        </is>
-      </c>
-      <c r="L12" s="2" t="inlineStr">
-        <is>
-          <t>9727</t>
-        </is>
-      </c>
-      <c r="M12" s="2" t="inlineStr">
-        <is>
-          <t>9727</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
@@ -8397,72 +8397,72 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="D13" s="2" t="inlineStr">
+        <is>
+          <t>663</t>
+        </is>
+      </c>
+      <c r="E13" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="F13" s="2" t="inlineStr">
+        <is>
+          <t>3441</t>
+        </is>
+      </c>
+      <c r="G13" s="2" t="inlineStr">
+        <is>
+          <t>2,24%</t>
+        </is>
+      </c>
+      <c r="H13" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="I13" s="2" t="inlineStr">
+        <is>
+          <t>11,62%</t>
+        </is>
+      </c>
+      <c r="J13" s="2" t="inlineStr">
+        <is>
           <t>2</t>
         </is>
       </c>
-      <c r="D13" s="2" t="inlineStr">
+      <c r="K13" s="2" t="inlineStr">
         <is>
           <t>1149</t>
         </is>
       </c>
-      <c r="E13" s="2" t="inlineStr">
+      <c r="L13" s="2" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="F13" s="2" t="inlineStr">
-        <is>
-          <t>3654</t>
-        </is>
-      </c>
-      <c r="G13" s="2" t="inlineStr">
+      <c r="M13" s="2" t="inlineStr">
+        <is>
+          <t>3730</t>
+        </is>
+      </c>
+      <c r="N13" s="2" t="inlineStr">
         <is>
           <t>3,29%</t>
         </is>
       </c>
-      <c r="H13" s="2" t="inlineStr">
+      <c r="O13" s="2" t="inlineStr">
         <is>
           <t>0,0%</t>
         </is>
       </c>
-      <c r="I13" s="2" t="inlineStr">
-        <is>
-          <t>10,47%</t>
-        </is>
-      </c>
-      <c r="J13" s="2" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="K13" s="2" t="inlineStr">
-        <is>
-          <t>663</t>
-        </is>
-      </c>
-      <c r="L13" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="M13" s="2" t="inlineStr">
-        <is>
-          <t>3271</t>
-        </is>
-      </c>
-      <c r="N13" s="2" t="inlineStr">
-        <is>
-          <t>2,24%</t>
-        </is>
-      </c>
-      <c r="O13" s="2" t="inlineStr">
-        <is>
-          <t>0,0%</t>
-        </is>
-      </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>11,05%</t>
+          <t>10,68%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -8477,12 +8477,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>550</t>
+          <t>561</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>5125</t>
+          <t>4846</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -8492,12 +8492,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>0,85%</t>
+          <t>0,87%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>7,94%</t>
+          <t>7,51%</t>
         </is>
       </c>
     </row>
@@ -8510,74 +8510,74 @@
       </c>
       <c r="C14" s="2" t="inlineStr">
         <is>
+          <t>39</t>
+        </is>
+      </c>
+      <c r="D14" s="2" t="inlineStr">
+        <is>
+          <t>28949</t>
+        </is>
+      </c>
+      <c r="E14" s="2" t="inlineStr">
+        <is>
+          <t>26171</t>
+        </is>
+      </c>
+      <c r="F14" s="2" t="inlineStr">
+        <is>
+          <t>29612</t>
+        </is>
+      </c>
+      <c r="G14" s="2" t="inlineStr">
+        <is>
+          <t>97,76%</t>
+        </is>
+      </c>
+      <c r="H14" s="2" t="inlineStr">
+        <is>
+          <t>88,38%</t>
+        </is>
+      </c>
+      <c r="I14" s="2" t="inlineStr">
+        <is>
+          <t>100,0%</t>
+        </is>
+      </c>
+      <c r="J14" s="2" t="inlineStr">
+        <is>
           <t>49</t>
         </is>
       </c>
-      <c r="D14" s="2" t="inlineStr">
+      <c r="K14" s="2" t="inlineStr">
         <is>
           <t>33766</t>
         </is>
       </c>
-      <c r="E14" s="2" t="inlineStr">
-        <is>
-          <t>31261</t>
-        </is>
-      </c>
-      <c r="F14" s="2" t="inlineStr">
+      <c r="L14" s="2" t="inlineStr">
+        <is>
+          <t>31185</t>
+        </is>
+      </c>
+      <c r="M14" s="2" t="inlineStr">
         <is>
           <t>34915</t>
         </is>
       </c>
-      <c r="G14" s="2" t="inlineStr">
+      <c r="N14" s="2" t="inlineStr">
         <is>
           <t>96,71%</t>
         </is>
       </c>
-      <c r="H14" s="2" t="inlineStr">
-        <is>
-          <t>89,53%</t>
-        </is>
-      </c>
-      <c r="I14" s="2" t="inlineStr">
+      <c r="O14" s="2" t="inlineStr">
+        <is>
+          <t>89,32%</t>
+        </is>
+      </c>
+      <c r="P14" s="2" t="inlineStr">
         <is>
           <t>100,0%</t>
         </is>
       </c>
-      <c r="J14" s="2" t="inlineStr">
-        <is>
-          <t>39</t>
-        </is>
-      </c>
-      <c r="K14" s="2" t="inlineStr">
-        <is>
-          <t>28949</t>
-        </is>
-      </c>
-      <c r="L14" s="2" t="inlineStr">
-        <is>
-          <t>26341</t>
-        </is>
-      </c>
-      <c r="M14" s="2" t="inlineStr">
-        <is>
-          <t>29612</t>
-        </is>
-      </c>
-      <c r="N14" s="2" t="inlineStr">
-        <is>
-          <t>97,76%</t>
-        </is>
-      </c>
-      <c r="O14" s="2" t="inlineStr">
-        <is>
-          <t>88,95%</t>
-        </is>
-      </c>
-      <c r="P14" s="2" t="inlineStr">
-        <is>
-          <t>100,0%</t>
-        </is>
-      </c>
       <c r="Q14" s="2" t="inlineStr">
         <is>
           <t>88</t>
@@ -8590,12 +8590,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>59402</t>
+          <t>59681</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>63977</t>
+          <t>63966</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -8605,12 +8605,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>92,06%</t>
+          <t>92,49%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>99,15%</t>
+          <t>99,13%</t>
         </is>
       </c>
     </row>
@@ -8623,57 +8623,57 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
+          <t>40</t>
+        </is>
+      </c>
+      <c r="D15" s="2" t="inlineStr">
+        <is>
+          <t>29612</t>
+        </is>
+      </c>
+      <c r="E15" s="2" t="inlineStr">
+        <is>
+          <t>29612</t>
+        </is>
+      </c>
+      <c r="F15" s="2" t="inlineStr">
+        <is>
+          <t>29612</t>
+        </is>
+      </c>
+      <c r="G15" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H15" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I15" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J15" s="2" t="inlineStr">
+        <is>
           <t>51</t>
         </is>
       </c>
-      <c r="D15" s="2" t="inlineStr">
+      <c r="K15" s="2" t="inlineStr">
         <is>
           <t>34915</t>
         </is>
       </c>
-      <c r="E15" s="2" t="inlineStr">
+      <c r="L15" s="2" t="inlineStr">
         <is>
           <t>34915</t>
         </is>
       </c>
-      <c r="F15" s="2" t="inlineStr">
+      <c r="M15" s="2" t="inlineStr">
         <is>
           <t>34915</t>
-        </is>
-      </c>
-      <c r="G15" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H15" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I15" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J15" s="2" t="inlineStr">
-        <is>
-          <t>40</t>
-        </is>
-      </c>
-      <c r="K15" s="2" t="inlineStr">
-        <is>
-          <t>29612</t>
-        </is>
-      </c>
-      <c r="L15" s="2" t="inlineStr">
-        <is>
-          <t>29612</t>
-        </is>
-      </c>
-      <c r="M15" s="2" t="inlineStr">
-        <is>
-          <t>29612</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
@@ -8858,42 +8858,42 @@
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
+          <t>7262</t>
+        </is>
+      </c>
+      <c r="E17" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="F17" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G17" s="2" t="inlineStr">
+        <is>
+          <t>100,0%</t>
+        </is>
+      </c>
+      <c r="H17" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="I17" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="J17" s="2" t="inlineStr">
+        <is>
+          <t>11</t>
+        </is>
+      </c>
+      <c r="K17" s="2" t="inlineStr">
+        <is>
           <t>7779</t>
-        </is>
-      </c>
-      <c r="E17" s="2" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="F17" s="2" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="G17" s="2" t="inlineStr">
-        <is>
-          <t>100,0%</t>
-        </is>
-      </c>
-      <c r="H17" s="2" t="inlineStr">
-        <is>
-          <t>—%</t>
-        </is>
-      </c>
-      <c r="I17" s="2" t="inlineStr">
-        <is>
-          <t>—%</t>
-        </is>
-      </c>
-      <c r="J17" s="2" t="inlineStr">
-        <is>
-          <t>11</t>
-        </is>
-      </c>
-      <c r="K17" s="2" t="inlineStr">
-        <is>
-          <t>7262</t>
         </is>
       </c>
       <c r="L17" s="2" t="inlineStr">
@@ -8971,52 +8971,52 @@
       </c>
       <c r="D18" s="2" t="inlineStr">
         <is>
+          <t>7262</t>
+        </is>
+      </c>
+      <c r="E18" s="2" t="inlineStr">
+        <is>
+          <t>7262</t>
+        </is>
+      </c>
+      <c r="F18" s="2" t="inlineStr">
+        <is>
+          <t>7262</t>
+        </is>
+      </c>
+      <c r="G18" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H18" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I18" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J18" s="2" t="inlineStr">
+        <is>
+          <t>11</t>
+        </is>
+      </c>
+      <c r="K18" s="2" t="inlineStr">
+        <is>
           <t>7779</t>
         </is>
       </c>
-      <c r="E18" s="2" t="inlineStr">
+      <c r="L18" s="2" t="inlineStr">
         <is>
           <t>7779</t>
         </is>
       </c>
-      <c r="F18" s="2" t="inlineStr">
+      <c r="M18" s="2" t="inlineStr">
         <is>
           <t>7779</t>
-        </is>
-      </c>
-      <c r="G18" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H18" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I18" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J18" s="2" t="inlineStr">
-        <is>
-          <t>11</t>
-        </is>
-      </c>
-      <c r="K18" s="2" t="inlineStr">
-        <is>
-          <t>7262</t>
-        </is>
-      </c>
-      <c r="L18" s="2" t="inlineStr">
-        <is>
-          <t>7262</t>
-        </is>
-      </c>
-      <c r="M18" s="2" t="inlineStr">
-        <is>
-          <t>7262</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
@@ -9196,47 +9196,47 @@
       </c>
       <c r="C20" s="2" t="inlineStr">
         <is>
+          <t>13</t>
+        </is>
+      </c>
+      <c r="D20" s="2" t="inlineStr">
+        <is>
+          <t>9475</t>
+        </is>
+      </c>
+      <c r="E20" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="F20" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G20" s="2" t="inlineStr">
+        <is>
+          <t>100,0%</t>
+        </is>
+      </c>
+      <c r="H20" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="I20" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="J20" s="2" t="inlineStr">
+        <is>
           <t>15</t>
         </is>
       </c>
-      <c r="D20" s="2" t="inlineStr">
+      <c r="K20" s="2" t="inlineStr">
         <is>
           <t>10580</t>
-        </is>
-      </c>
-      <c r="E20" s="2" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="F20" s="2" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="G20" s="2" t="inlineStr">
-        <is>
-          <t>100,0%</t>
-        </is>
-      </c>
-      <c r="H20" s="2" t="inlineStr">
-        <is>
-          <t>—%</t>
-        </is>
-      </c>
-      <c r="I20" s="2" t="inlineStr">
-        <is>
-          <t>—%</t>
-        </is>
-      </c>
-      <c r="J20" s="2" t="inlineStr">
-        <is>
-          <t>13</t>
-        </is>
-      </c>
-      <c r="K20" s="2" t="inlineStr">
-        <is>
-          <t>9475</t>
         </is>
       </c>
       <c r="L20" s="2" t="inlineStr">
@@ -9309,57 +9309,57 @@
       </c>
       <c r="C21" s="2" t="inlineStr">
         <is>
+          <t>13</t>
+        </is>
+      </c>
+      <c r="D21" s="2" t="inlineStr">
+        <is>
+          <t>9475</t>
+        </is>
+      </c>
+      <c r="E21" s="2" t="inlineStr">
+        <is>
+          <t>9475</t>
+        </is>
+      </c>
+      <c r="F21" s="2" t="inlineStr">
+        <is>
+          <t>9475</t>
+        </is>
+      </c>
+      <c r="G21" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H21" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I21" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J21" s="2" t="inlineStr">
+        <is>
           <t>15</t>
         </is>
       </c>
-      <c r="D21" s="2" t="inlineStr">
+      <c r="K21" s="2" t="inlineStr">
         <is>
           <t>10580</t>
         </is>
       </c>
-      <c r="E21" s="2" t="inlineStr">
+      <c r="L21" s="2" t="inlineStr">
         <is>
           <t>10580</t>
         </is>
       </c>
-      <c r="F21" s="2" t="inlineStr">
+      <c r="M21" s="2" t="inlineStr">
         <is>
           <t>10580</t>
-        </is>
-      </c>
-      <c r="G21" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H21" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I21" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J21" s="2" t="inlineStr">
-        <is>
-          <t>13</t>
-        </is>
-      </c>
-      <c r="K21" s="2" t="inlineStr">
-        <is>
-          <t>9475</t>
-        </is>
-      </c>
-      <c r="L21" s="2" t="inlineStr">
-        <is>
-          <t>9475</t>
-        </is>
-      </c>
-      <c r="M21" s="2" t="inlineStr">
-        <is>
-          <t>9475</t>
         </is>
       </c>
       <c r="N21" s="2" t="inlineStr">
@@ -9426,107 +9426,107 @@
       </c>
       <c r="C22" s="2" t="inlineStr">
         <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="D22" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="E22" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="F22" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G22" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="H22" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="I22" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="J22" s="2" t="inlineStr">
+        <is>
           <t>1</t>
         </is>
       </c>
-      <c r="D22" s="2" t="inlineStr">
+      <c r="K22" s="2" t="inlineStr">
         <is>
           <t>613</t>
         </is>
       </c>
-      <c r="E22" s="2" t="inlineStr">
+      <c r="L22" s="2" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="F22" s="2" t="inlineStr">
-        <is>
-          <t>3102</t>
-        </is>
-      </c>
-      <c r="G22" s="2" t="inlineStr">
+      <c r="M22" s="2" t="inlineStr">
+        <is>
+          <t>3089</t>
+        </is>
+      </c>
+      <c r="N22" s="2" t="inlineStr">
         <is>
           <t>3,11%</t>
         </is>
       </c>
-      <c r="H22" s="2" t="inlineStr">
+      <c r="O22" s="2" t="inlineStr">
         <is>
           <t>0,0%</t>
         </is>
       </c>
-      <c r="I22" s="2" t="inlineStr">
-        <is>
-          <t>15,73%</t>
-        </is>
-      </c>
-      <c r="J22" s="2" t="inlineStr">
+      <c r="P22" s="2" t="inlineStr">
+        <is>
+          <t>15,67%</t>
+        </is>
+      </c>
+      <c r="Q22" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="R22" s="2" t="inlineStr">
+        <is>
+          <t>613</t>
+        </is>
+      </c>
+      <c r="S22" s="2" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="K22" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="L22" s="2" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="M22" s="2" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="N22" s="2" t="inlineStr">
+      <c r="T22" s="2" t="inlineStr">
+        <is>
+          <t>3511</t>
+        </is>
+      </c>
+      <c r="U22" s="2" t="inlineStr">
+        <is>
+          <t>1,82%</t>
+        </is>
+      </c>
+      <c r="V22" s="2" t="inlineStr">
         <is>
           <t>0,0%</t>
         </is>
       </c>
-      <c r="O22" s="2" t="inlineStr">
-        <is>
-          <t>—%</t>
-        </is>
-      </c>
-      <c r="P22" s="2" t="inlineStr">
-        <is>
-          <t>—%</t>
-        </is>
-      </c>
-      <c r="Q22" s="2" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="R22" s="2" t="inlineStr">
-        <is>
-          <t>613</t>
-        </is>
-      </c>
-      <c r="S22" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="T22" s="2" t="inlineStr">
-        <is>
-          <t>3065</t>
-        </is>
-      </c>
-      <c r="U22" s="2" t="inlineStr">
-        <is>
-          <t>1,82%</t>
-        </is>
-      </c>
-      <c r="V22" s="2" t="inlineStr">
-        <is>
-          <t>0,0%</t>
-        </is>
-      </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>9,1%</t>
+          <t>10,43%</t>
         </is>
       </c>
     </row>
@@ -9539,74 +9539,74 @@
       </c>
       <c r="C23" s="2" t="inlineStr">
         <is>
+          <t>21</t>
+        </is>
+      </c>
+      <c r="D23" s="2" t="inlineStr">
+        <is>
+          <t>13964</t>
+        </is>
+      </c>
+      <c r="E23" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="F23" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G23" s="2" t="inlineStr">
+        <is>
+          <t>100,0%</t>
+        </is>
+      </c>
+      <c r="H23" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="I23" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="J23" s="2" t="inlineStr">
+        <is>
           <t>29</t>
         </is>
       </c>
-      <c r="D23" s="2" t="inlineStr">
+      <c r="K23" s="2" t="inlineStr">
         <is>
           <t>19100</t>
         </is>
       </c>
-      <c r="E23" s="2" t="inlineStr">
-        <is>
-          <t>16611</t>
-        </is>
-      </c>
-      <c r="F23" s="2" t="inlineStr">
+      <c r="L23" s="2" t="inlineStr">
+        <is>
+          <t>16624</t>
+        </is>
+      </c>
+      <c r="M23" s="2" t="inlineStr">
         <is>
           <t>19713</t>
         </is>
       </c>
-      <c r="G23" s="2" t="inlineStr">
+      <c r="N23" s="2" t="inlineStr">
         <is>
           <t>96,89%</t>
         </is>
       </c>
-      <c r="H23" s="2" t="inlineStr">
-        <is>
-          <t>84,27%</t>
-        </is>
-      </c>
-      <c r="I23" s="2" t="inlineStr">
+      <c r="O23" s="2" t="inlineStr">
+        <is>
+          <t>84,33%</t>
+        </is>
+      </c>
+      <c r="P23" s="2" t="inlineStr">
         <is>
           <t>100,0%</t>
         </is>
       </c>
-      <c r="J23" s="2" t="inlineStr">
-        <is>
-          <t>21</t>
-        </is>
-      </c>
-      <c r="K23" s="2" t="inlineStr">
-        <is>
-          <t>13964</t>
-        </is>
-      </c>
-      <c r="L23" s="2" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="M23" s="2" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="N23" s="2" t="inlineStr">
-        <is>
-          <t>100,0%</t>
-        </is>
-      </c>
-      <c r="O23" s="2" t="inlineStr">
-        <is>
-          <t>—%</t>
-        </is>
-      </c>
-      <c r="P23" s="2" t="inlineStr">
-        <is>
-          <t>—%</t>
-        </is>
-      </c>
       <c r="Q23" s="2" t="inlineStr">
         <is>
           <t>50</t>
@@ -9619,7 +9619,7 @@
       </c>
       <c r="S23" s="2" t="inlineStr">
         <is>
-          <t>30612</t>
+          <t>30166</t>
         </is>
       </c>
       <c r="T23" s="2" t="inlineStr">
@@ -9634,7 +9634,7 @@
       </c>
       <c r="V23" s="2" t="inlineStr">
         <is>
-          <t>90,9%</t>
+          <t>89,57%</t>
         </is>
       </c>
       <c r="W23" s="2" t="inlineStr">
@@ -9652,57 +9652,57 @@
       </c>
       <c r="C24" s="2" t="inlineStr">
         <is>
+          <t>21</t>
+        </is>
+      </c>
+      <c r="D24" s="2" t="inlineStr">
+        <is>
+          <t>13964</t>
+        </is>
+      </c>
+      <c r="E24" s="2" t="inlineStr">
+        <is>
+          <t>13964</t>
+        </is>
+      </c>
+      <c r="F24" s="2" t="inlineStr">
+        <is>
+          <t>13964</t>
+        </is>
+      </c>
+      <c r="G24" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H24" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I24" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J24" s="2" t="inlineStr">
+        <is>
           <t>30</t>
         </is>
       </c>
-      <c r="D24" s="2" t="inlineStr">
+      <c r="K24" s="2" t="inlineStr">
         <is>
           <t>19713</t>
         </is>
       </c>
-      <c r="E24" s="2" t="inlineStr">
+      <c r="L24" s="2" t="inlineStr">
         <is>
           <t>19713</t>
         </is>
       </c>
-      <c r="F24" s="2" t="inlineStr">
+      <c r="M24" s="2" t="inlineStr">
         <is>
           <t>19713</t>
-        </is>
-      </c>
-      <c r="G24" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H24" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I24" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J24" s="2" t="inlineStr">
-        <is>
-          <t>21</t>
-        </is>
-      </c>
-      <c r="K24" s="2" t="inlineStr">
-        <is>
-          <t>13964</t>
-        </is>
-      </c>
-      <c r="L24" s="2" t="inlineStr">
-        <is>
-          <t>13964</t>
-        </is>
-      </c>
-      <c r="M24" s="2" t="inlineStr">
-        <is>
-          <t>13964</t>
         </is>
       </c>
       <c r="N24" s="2" t="inlineStr">
@@ -9882,47 +9882,47 @@
       </c>
       <c r="C26" s="2" t="inlineStr">
         <is>
+          <t>46</t>
+        </is>
+      </c>
+      <c r="D26" s="2" t="inlineStr">
+        <is>
+          <t>30267</t>
+        </is>
+      </c>
+      <c r="E26" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="F26" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G26" s="2" t="inlineStr">
+        <is>
+          <t>100,0%</t>
+        </is>
+      </c>
+      <c r="H26" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="I26" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="J26" s="2" t="inlineStr">
+        <is>
           <t>47</t>
         </is>
       </c>
-      <c r="D26" s="2" t="inlineStr">
+      <c r="K26" s="2" t="inlineStr">
         <is>
           <t>29294</t>
-        </is>
-      </c>
-      <c r="E26" s="2" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="F26" s="2" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="G26" s="2" t="inlineStr">
-        <is>
-          <t>100,0%</t>
-        </is>
-      </c>
-      <c r="H26" s="2" t="inlineStr">
-        <is>
-          <t>—%</t>
-        </is>
-      </c>
-      <c r="I26" s="2" t="inlineStr">
-        <is>
-          <t>—%</t>
-        </is>
-      </c>
-      <c r="J26" s="2" t="inlineStr">
-        <is>
-          <t>46</t>
-        </is>
-      </c>
-      <c r="K26" s="2" t="inlineStr">
-        <is>
-          <t>30267</t>
         </is>
       </c>
       <c r="L26" s="2" t="inlineStr">
@@ -9995,57 +9995,57 @@
       </c>
       <c r="C27" s="2" t="inlineStr">
         <is>
+          <t>46</t>
+        </is>
+      </c>
+      <c r="D27" s="2" t="inlineStr">
+        <is>
+          <t>30267</t>
+        </is>
+      </c>
+      <c r="E27" s="2" t="inlineStr">
+        <is>
+          <t>30267</t>
+        </is>
+      </c>
+      <c r="F27" s="2" t="inlineStr">
+        <is>
+          <t>30267</t>
+        </is>
+      </c>
+      <c r="G27" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H27" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I27" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J27" s="2" t="inlineStr">
+        <is>
           <t>47</t>
         </is>
       </c>
-      <c r="D27" s="2" t="inlineStr">
+      <c r="K27" s="2" t="inlineStr">
         <is>
           <t>29294</t>
         </is>
       </c>
-      <c r="E27" s="2" t="inlineStr">
+      <c r="L27" s="2" t="inlineStr">
         <is>
           <t>29294</t>
         </is>
       </c>
-      <c r="F27" s="2" t="inlineStr">
+      <c r="M27" s="2" t="inlineStr">
         <is>
           <t>29294</t>
-        </is>
-      </c>
-      <c r="G27" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H27" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I27" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J27" s="2" t="inlineStr">
-        <is>
-          <t>46</t>
-        </is>
-      </c>
-      <c r="K27" s="2" t="inlineStr">
-        <is>
-          <t>30267</t>
-        </is>
-      </c>
-      <c r="L27" s="2" t="inlineStr">
-        <is>
-          <t>30267</t>
-        </is>
-      </c>
-      <c r="M27" s="2" t="inlineStr">
-        <is>
-          <t>30267</t>
         </is>
       </c>
       <c r="N27" s="2" t="inlineStr">
@@ -10117,67 +10117,67 @@
       </c>
       <c r="D28" s="2" t="inlineStr">
         <is>
+          <t>2062</t>
+        </is>
+      </c>
+      <c r="E28" s="2" t="inlineStr">
+        <is>
+          <t>661</t>
+        </is>
+      </c>
+      <c r="F28" s="2" t="inlineStr">
+        <is>
+          <t>4881</t>
+        </is>
+      </c>
+      <c r="G28" s="2" t="inlineStr">
+        <is>
+          <t>1,39%</t>
+        </is>
+      </c>
+      <c r="H28" s="2" t="inlineStr">
+        <is>
+          <t>0,45%</t>
+        </is>
+      </c>
+      <c r="I28" s="2" t="inlineStr">
+        <is>
+          <t>3,3%</t>
+        </is>
+      </c>
+      <c r="J28" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="K28" s="2" t="inlineStr">
+        <is>
           <t>1762</t>
         </is>
       </c>
-      <c r="E28" s="2" t="inlineStr">
-        <is>
-          <t>557</t>
-        </is>
-      </c>
-      <c r="F28" s="2" t="inlineStr">
-        <is>
-          <t>4794</t>
-        </is>
-      </c>
-      <c r="G28" s="2" t="inlineStr">
+      <c r="L28" s="2" t="inlineStr">
+        <is>
+          <t>554</t>
+        </is>
+      </c>
+      <c r="M28" s="2" t="inlineStr">
+        <is>
+          <t>4830</t>
+        </is>
+      </c>
+      <c r="N28" s="2" t="inlineStr">
         <is>
           <t>1,08%</t>
         </is>
       </c>
-      <c r="H28" s="2" t="inlineStr">
+      <c r="O28" s="2" t="inlineStr">
         <is>
           <t>0,34%</t>
         </is>
       </c>
-      <c r="I28" s="2" t="inlineStr">
-        <is>
-          <t>2,95%</t>
-        </is>
-      </c>
-      <c r="J28" s="2" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
-      <c r="K28" s="2" t="inlineStr">
-        <is>
-          <t>2062</t>
-        </is>
-      </c>
-      <c r="L28" s="2" t="inlineStr">
-        <is>
-          <t>656</t>
-        </is>
-      </c>
-      <c r="M28" s="2" t="inlineStr">
-        <is>
-          <t>5618</t>
-        </is>
-      </c>
-      <c r="N28" s="2" t="inlineStr">
-        <is>
-          <t>1,39%</t>
-        </is>
-      </c>
-      <c r="O28" s="2" t="inlineStr">
-        <is>
-          <t>0,44%</t>
-        </is>
-      </c>
       <c r="P28" s="2" t="inlineStr">
         <is>
-          <t>3,79%</t>
+          <t>2,97%</t>
         </is>
       </c>
       <c r="Q28" s="2" t="inlineStr">
@@ -10192,12 +10192,12 @@
       </c>
       <c r="S28" s="2" t="inlineStr">
         <is>
-          <t>1393</t>
+          <t>1392</t>
         </is>
       </c>
       <c r="T28" s="2" t="inlineStr">
         <is>
-          <t>7846</t>
+          <t>7948</t>
         </is>
       </c>
       <c r="U28" s="2" t="inlineStr">
@@ -10212,7 +10212,7 @@
       </c>
       <c r="W28" s="2" t="inlineStr">
         <is>
-          <t>2,53%</t>
+          <t>2,56%</t>
         </is>
       </c>
     </row>
@@ -10225,74 +10225,74 @@
       </c>
       <c r="C29" s="2" t="inlineStr">
         <is>
+          <t>212</t>
+        </is>
+      </c>
+      <c r="D29" s="2" t="inlineStr">
+        <is>
+          <t>146063</t>
+        </is>
+      </c>
+      <c r="E29" s="2" t="inlineStr">
+        <is>
+          <t>143244</t>
+        </is>
+      </c>
+      <c r="F29" s="2" t="inlineStr">
+        <is>
+          <t>147464</t>
+        </is>
+      </c>
+      <c r="G29" s="2" t="inlineStr">
+        <is>
+          <t>98,61%</t>
+        </is>
+      </c>
+      <c r="H29" s="2" t="inlineStr">
+        <is>
+          <t>96,7%</t>
+        </is>
+      </c>
+      <c r="I29" s="2" t="inlineStr">
+        <is>
+          <t>99,55%</t>
+        </is>
+      </c>
+      <c r="J29" s="2" t="inlineStr">
+        <is>
           <t>242</t>
         </is>
       </c>
-      <c r="D29" s="2" t="inlineStr">
+      <c r="K29" s="2" t="inlineStr">
         <is>
           <t>160774</t>
         </is>
       </c>
-      <c r="E29" s="2" t="inlineStr">
-        <is>
-          <t>157742</t>
-        </is>
-      </c>
-      <c r="F29" s="2" t="inlineStr">
-        <is>
-          <t>161979</t>
-        </is>
-      </c>
-      <c r="G29" s="2" t="inlineStr">
+      <c r="L29" s="2" t="inlineStr">
+        <is>
+          <t>157706</t>
+        </is>
+      </c>
+      <c r="M29" s="2" t="inlineStr">
+        <is>
+          <t>161982</t>
+        </is>
+      </c>
+      <c r="N29" s="2" t="inlineStr">
         <is>
           <t>98,92%</t>
         </is>
       </c>
-      <c r="H29" s="2" t="inlineStr">
-        <is>
-          <t>97,05%</t>
-        </is>
-      </c>
-      <c r="I29" s="2" t="inlineStr">
+      <c r="O29" s="2" t="inlineStr">
+        <is>
+          <t>97,03%</t>
+        </is>
+      </c>
+      <c r="P29" s="2" t="inlineStr">
         <is>
           <t>99,66%</t>
         </is>
       </c>
-      <c r="J29" s="2" t="inlineStr">
-        <is>
-          <t>212</t>
-        </is>
-      </c>
-      <c r="K29" s="2" t="inlineStr">
-        <is>
-          <t>146063</t>
-        </is>
-      </c>
-      <c r="L29" s="2" t="inlineStr">
-        <is>
-          <t>142507</t>
-        </is>
-      </c>
-      <c r="M29" s="2" t="inlineStr">
-        <is>
-          <t>147469</t>
-        </is>
-      </c>
-      <c r="N29" s="2" t="inlineStr">
-        <is>
-          <t>98,61%</t>
-        </is>
-      </c>
-      <c r="O29" s="2" t="inlineStr">
-        <is>
-          <t>96,21%</t>
-        </is>
-      </c>
-      <c r="P29" s="2" t="inlineStr">
-        <is>
-          <t>99,56%</t>
-        </is>
-      </c>
       <c r="Q29" s="2" t="inlineStr">
         <is>
           <t>454</t>
@@ -10305,12 +10305,12 @@
       </c>
       <c r="S29" s="2" t="inlineStr">
         <is>
-          <t>302815</t>
+          <t>302713</t>
         </is>
       </c>
       <c r="T29" s="2" t="inlineStr">
         <is>
-          <t>309268</t>
+          <t>309269</t>
         </is>
       </c>
       <c r="U29" s="2" t="inlineStr">
@@ -10320,7 +10320,7 @@
       </c>
       <c r="V29" s="2" t="inlineStr">
         <is>
-          <t>97,47%</t>
+          <t>97,44%</t>
         </is>
       </c>
       <c r="W29" s="2" t="inlineStr">
@@ -10338,57 +10338,57 @@
       </c>
       <c r="C30" s="2" t="inlineStr">
         <is>
+          <t>215</t>
+        </is>
+      </c>
+      <c r="D30" s="2" t="inlineStr">
+        <is>
+          <t>148125</t>
+        </is>
+      </c>
+      <c r="E30" s="2" t="inlineStr">
+        <is>
+          <t>148125</t>
+        </is>
+      </c>
+      <c r="F30" s="2" t="inlineStr">
+        <is>
+          <t>148125</t>
+        </is>
+      </c>
+      <c r="G30" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H30" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I30" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J30" s="2" t="inlineStr">
+        <is>
           <t>245</t>
         </is>
       </c>
-      <c r="D30" s="2" t="inlineStr">
+      <c r="K30" s="2" t="inlineStr">
         <is>
           <t>162536</t>
         </is>
       </c>
-      <c r="E30" s="2" t="inlineStr">
+      <c r="L30" s="2" t="inlineStr">
         <is>
           <t>162536</t>
         </is>
       </c>
-      <c r="F30" s="2" t="inlineStr">
+      <c r="M30" s="2" t="inlineStr">
         <is>
           <t>162536</t>
-        </is>
-      </c>
-      <c r="G30" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H30" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I30" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J30" s="2" t="inlineStr">
-        <is>
-          <t>215</t>
-        </is>
-      </c>
-      <c r="K30" s="2" t="inlineStr">
-        <is>
-          <t>148125</t>
-        </is>
-      </c>
-      <c r="L30" s="2" t="inlineStr">
-        <is>
-          <t>148125</t>
-        </is>
-      </c>
-      <c r="M30" s="2" t="inlineStr">
-        <is>
-          <t>148125</t>
         </is>
       </c>
       <c r="N30" s="2" t="inlineStr">
